--- a/output/TFL_TOC_v2.1.0.xlsx
+++ b/output/TFL_TOC_v2.1.0.xlsx
@@ -18,12 +18,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOC_Master'!$A$1:$M$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOC_Master'!$A$1:$M$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'14.1_Demographics'!$A$1:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'14.2_Efficacy'!$A$1:$M$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'14.3_Safety'!$A$1:$M$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'14.4_Special'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'16.2_Listings'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'14.4_Special'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'16.2_Listings'!$A$1:$M$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Field_Definitions'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Usage_Guide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Change_Log'!$A$1:$E$2</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,11 +628,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Continuous: n, Mean, SD, Median, Min, Max. Categorical: n (%).</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -741,7 +737,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -804,7 +800,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>WHO-DD 2024Q1</t>
+          <t>WHO-DD [version]</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1044,7 +1040,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1107,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>WHO-DD 2024Q1</t>
+          <t>WHO-DD [version]</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1194,7 +1190,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Summary of Study Drug Exposure</t>
+          <t>Summary of Study Drug Exposure — Duration, Cycles, Dose Intensity</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1504,7 +1500,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>ITT and Per-Protocol (PP) Populations</t>
+          <t>ITT and PP Populations</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1910,7 +1906,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Cumulative Distribution Function Plot</t>
+          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2610,145 +2606,137 @@
       <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.4</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.4</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.20</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.20</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>ITT Alive and On-Study at 6 Months</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADRS</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>f_waterfall.sas</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>t_landmark_os.sas</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.5</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.5</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.21</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.21</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Time to First Subsequent Therapy (TFST)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>ITT with Measurable Disease</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADRS</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>f_spider.sas</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE, ADCM</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>t_tfst.sas</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>F14.2.6</t>
+          <t>F14.2.4</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.6</t>
+          <t>Figure 14.2.4</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Swimmer Plot — Duration of Treatment and Response</t>
+          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2763,7 +2751,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2773,12 +2761,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADEX, ADRS</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>f_swimmer.sas</t>
+          <t>f_waterfall.sas</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
@@ -2801,17 +2789,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>F14.2.7</t>
+          <t>F14.2.5</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.7</t>
+          <t>Figure 14.2.5</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
+          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2826,7 +2814,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT with Measurable Disease</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2836,12 +2824,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>f_km_pfs.sas</t>
+          <t>f_spider.sas</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2864,17 +2852,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>F14.2.8</t>
+          <t>F14.2.6</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.8</t>
+          <t>Figure 14.2.6</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Overall Survival</t>
+          <t>Swimmer Plot — Duration of Treatment and Response</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -2889,7 +2877,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2899,12 +2887,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADEX, ADRS</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>f_km_os.sas</t>
+          <t>f_swimmer.sas</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
@@ -2927,17 +2915,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>F14.2.9</t>
+          <t>F14.2.7</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.9</t>
+          <t>Figure 14.2.7</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — PFS by Subgroup</t>
+          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2967,7 +2955,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>f_forest_pfs.sas</t>
+          <t>f_km_pfs.sas</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -2990,17 +2978,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>F14.2.10</t>
+          <t>F14.2.8</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.10</t>
+          <t>Figure 14.2.8</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — OS by Subgroup</t>
+          <t>Kaplan-Meier Plot — Overall Survival</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3030,7 +3018,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>f_forest_os.sas</t>
+          <t>f_km_os.sas</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr"/>
@@ -3051,122 +3039,130 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.20</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.20</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.9</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.9</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — PFS by Subgroup</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>ITT Alive and On-Study at 6 Months</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADTTE</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>t_landmark_os.sas</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_pfs.sas</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.21</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.21</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Exposure-Response Correlation</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.10</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.10</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — OS by Subgroup</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Evaluable Population</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPK, ADEFF</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>t_pkpd_corr.sas</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_os.sas</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3181,7 +3177,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Time to First Subsequent Therapy (TFST)</t>
+          <t>PK/PD Exposure-Response Correlation Analysis</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3196,22 +3192,22 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>PK/PD Evaluable Population</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE, ADCM</t>
+          <t>ADSL, ADPK, ADEFF</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>t_tfst.sas</t>
+          <t>t_pkpd_corr.sas</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -3275,7 +3271,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3338,7 +3334,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3366,7 +3362,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by SOC, PT, and Maximum CTCAE Grade (Treatment A)</t>
+          <t>TEAEs by SOC, PT, and Maximum CTCAE Grade (Group 1)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3401,7 +3397,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3464,7 +3460,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3527,7 +3523,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3590,7 +3586,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3653,7 +3649,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3681,7 +3677,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>TEAEs Leading to Death (Grade 5)</t>
+          <t>Summary of Deaths</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3706,19 +3702,15 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL, ADAE, ADTTE</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>l_ae_death.sas</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>t_deaths.sas</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -3779,7 +3771,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3842,7 +3834,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3905,7 +3897,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3933,7 +3925,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by Age Group Subgroup (&gt;=5% in Any Arm)</t>
+          <t>TEAEs by Age Group Subgroup</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3968,7 +3960,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3996,7 +3988,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by Sex Subgroup (&gt;=5% in Any Arm)</t>
+          <t>TEAEs by Sex Subgroup</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4031,7 +4023,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4059,7 +4051,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Listing of All Deaths with Narrative Reference</t>
+          <t>Hy's Law Cases — Liver Chemistry Screening</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4074,7 +4066,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>All Randomized Subjects</t>
+          <t>Safety Population with Baseline and Post-Baseline Labs</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4084,12 +4076,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADTTE</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>l_deaths.sas</t>
+          <t>t_hys_law.sas</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -4118,7 +4110,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Hy's Law Cases — Liver Chemistry Screening</t>
+          <t>Laboratory Parameters — Shift Table (Baseline to Worst Post-Baseline)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4133,7 +4125,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with Baseline and Post-Baseline Labs</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -4148,10 +4140,14 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>t_hys_law.sas</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr"/>
+          <t>t_lab_shift.sas</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4177,7 +4173,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Parameters — Shift Table (Baseline to Worst Post-Baseline)</t>
+          <t>Hematology Parameters — Summary Statistics by Visit</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4207,14 +4203,10 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>t_lab_shift.sas</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>t_heme_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4240,7 +4232,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Hematology Parameters — Summary Statistics by Visit</t>
+          <t>Clinical Chemistry Parameters — Summary Statistics by Visit</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4270,7 +4262,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>t_heme_by_visit.sas</t>
+          <t>t_chem_by_visit.sas</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -4299,7 +4291,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Clinical Chemistry Parameters — Summary Statistics by Visit</t>
+          <t>Laboratory Abnormalities — Grade &gt;=3 Listing</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4329,10 +4321,14 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>t_chem_by_visit.sas</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr"/>
+          <t>l_lab_grade3.sas</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4358,7 +4354,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Abnormalities — Grade &gt;=3 Listing</t>
+          <t>Laboratory Toxicity Grade Shift Over Time (by Cycle)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4388,12 +4384,12 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>l_lab_grade3.sas</t>
+          <t>t_lab_shift_cycle.sas</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>CTCAE 5.0</t>
+          <t>CTCAE [xx]</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4409,82 +4405,82 @@
       <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>T14.3.20</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.3.20</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Laboratory Toxicity Grade Shift Over Time (by Cycle)</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>F14.3.1</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.3.1</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Mean (+/- SD) Change in Laboratory Parameters Over Time</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADLB</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>t_lab_shift_cycle.sas</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>CTCAE 5.0</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>f_lab_longitudinal.sas</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>F14.3.1</t>
+          <t>F14.3.2</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.3.1</t>
+          <t>Figure 14.3.2</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Mean (+/- SD) Change in Laboratory Parameters Over Time</t>
+          <t>Box Plot — Liver Function Tests by Visit</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -4514,7 +4510,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>f_lab_longitudinal.sas</t>
+          <t>f_lft_box.sas</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr"/>
@@ -4535,67 +4531,63 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>F14.3.2</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.3.2</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Box Plot — Liver Function Tests by Visit</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.20</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.20</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Vital Signs — Summary Statistics by Visit</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADLB</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>f_lft_box.sas</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr"/>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>t_vs_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4610,7 +4602,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Vital Signs — Summary Statistics by Visit</t>
+          <t>Vital Signs — Clinically Notable Abnormalities by Visit</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4640,7 +4632,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>t_vs_by_visit.sas</t>
+          <t>t_vs_notable.sas</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -4657,78 +4649,82 @@
       <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>T14.3.22</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.3.22</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Vital Signs — Clinically Notable Abnormalities by Visit</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>F14.3.3</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.3.3</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Mean (+/- SD) Vital Signs Over Time</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADVS</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>t_vs_notable.sas</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>f_vs_longitudinal.sas</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>F14.3.3</t>
+          <t>F14.3.4</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.3.3</t>
+          <t>Figure 14.3.4</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Mean (+/- SD) Vital Signs Over Time</t>
+          <t>Liver Function Panel — Mean Over Time with ULN Reference</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4753,12 +4749,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADVS</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>f_vs_longitudinal.sas</t>
+          <t>f_lft_uln.sas</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr"/>
@@ -4779,67 +4775,63 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>F14.3.4</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.3.4</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Liver Function Panel — Mean Over Time with ULN Reference</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.22</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.22</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>ECG Parameters — Summary Statistics by Visit</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADLB</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>f_lft_uln.sas</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr"/>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ECG Data</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADEG</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>t_ecg_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4854,7 +4846,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ECG Parameters — Summary Statistics by Visit</t>
+          <t>ECG QTcF Categorical Analysis</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4884,7 +4876,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>t_ecg_by_visit.sas</t>
+          <t>t_qtcf_cat.sas</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -4913,7 +4905,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ECG QTcF Categorical Analysis</t>
+          <t>ECG Qualitative Assessment — Shift Table</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4943,7 +4935,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>t_qtcf_cat.sas</t>
+          <t>t_ecg_shift.sas</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -4972,7 +4964,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>ECG Qualitative Assessment — Shift Table</t>
+          <t>Infusion-Related Reactions by Preferred Term</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4987,7 +4979,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ECG Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4997,15 +4989,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEG</t>
+          <t>ADSL, ADAE, ADEX</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>t_ecg_shift.sas</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+          <t>t_irr.sas</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5031,7 +5027,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Infusion-Related Reactions by Preferred Term</t>
+          <t>ECOG Performance Status Shift Table</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5056,19 +5052,15 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADEX</t>
+          <t>ADSL, ADQS</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>t_irr.sas</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>t_ecog_shift.sas</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5153,7 +5145,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Summary of PK Parameters by Subject</t>
+          <t>Summary of Pharmacokinetic Parameters</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5200,78 +5192,78 @@
       <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.1</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.1</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Pharmacokinetic Concentrations by Subject and Timepoint</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.3</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.3</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Anti-Drug Antibody (ADA) Incidence</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>l_pk_conc.sas</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr"/>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M78" s="4" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>t_ada_incidence.sas</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>T14.4.3</t>
+          <t>T14.4.4</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.3</t>
+          <t>Table 14.4.4</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Immunogenicity Summary — Anti-Drug Antibody (ADA) Incidence</t>
+          <t>Summary of Biomarker Results by Visit</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5286,7 +5278,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>ITT Population with Biomarker Data</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -5296,12 +5288,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>t_ada_incidence.sas</t>
+          <t>t_biomarker_visit.sas</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -5318,78 +5310,78 @@
       <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.2</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.2</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Immunogenicity Results by Subject and Visit</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.5</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.5</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Patient-Reported Outcomes by Visit</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population with ADA Samples</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADIS</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>l_immuno.sas</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr"/>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M80" s="4" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population with PRO Data</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>t_pro_summary.sas</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>T14.4.4</t>
+          <t>T14.4.6</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.4</t>
+          <t>Table 14.4.6</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Summary of Biomarker Results by Visit</t>
+          <t>Summary of Pharmacodynamics — Soluble Biomarkers by Visit</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5404,7 +5396,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>ITT Population with Biomarker Data</t>
+          <t>PD Population</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -5414,12 +5406,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, ADPD</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>t_biomarker_visit.sas</t>
+          <t>t_pd_summary.sas</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -5436,314 +5428,330 @@
       <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.3</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.3</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Biomarker Results by Subject and Visit</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.7</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.7</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Central Molecular Test Results and Gene Aberrations at Baseline</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>ITT with Biomarker Data</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Full Analysis Set</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>ADSL, ADBM</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>l_biomarker.sas</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M82" s="4" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>t_gene_aberrations.sas</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.5</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.5</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Summary of Patient-Reported Outcomes by Visit</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.1</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.1</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>ITT Population with PRO Data</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPRO</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>t_pro_summary.sas</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_profile.sas</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.4</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.4</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Patient-Reported Outcomes by Subject and Visit</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.2</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.2</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Overlaying Individual PK Concentration Profiles</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>ITT with PRO Data</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADPRO</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>l_pro.sas</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M84" s="4" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_overlay.sas</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.1</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.1</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Subject Disposition</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>All Randomized Subjects</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>l_disposition.sas</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr"/>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M85" s="4" t="inlineStr"/>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.3</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.3</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>PD Population</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPD</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>f_pd_time.sas</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.2</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.2</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Demographic Data</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>All Randomized Subjects</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>l_demog.sas</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M86" s="4" t="inlineStr"/>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.4</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.4</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Boxplot of Biomarkers at Baseline vs. Response Status</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Full Analysis Set with Biomarker Data</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADBM</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>f_biomarker_box.sas</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>L16.2.3</t>
+          <t>L16.2.1</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.3</t>
+          <t>Listing 16.2.1</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Listing of Protocol Deviations</t>
+          <t>Listing of Subject Disposition</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -5758,7 +5766,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>All Randomized Subjects</t>
+          <t>All Screened Subjects</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -5768,12 +5776,12 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>ADSL, DV</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>l_protdev.sas</t>
+          <t>l_disposition.sas</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr"/>
@@ -5792,17 +5800,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>L16.2.4</t>
+          <t>L16.2.2</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.4</t>
+          <t>Listing 16.2.2</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Listing of Adverse Events</t>
+          <t>Listing of Demographic Data</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -5817,7 +5825,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>All Randomized Subjects</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -5827,19 +5835,15 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>l_ae.sas</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>l_demog.sas</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5855,17 +5859,17 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>L16.2.5</t>
+          <t>L16.2.3</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.5</t>
+          <t>Listing 16.2.3</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Listing of Serious Adverse Events</t>
+          <t>Listing of Protocol Deviations</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -5880,7 +5884,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>All Enrolled Subjects</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -5890,19 +5894,15 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL, DV</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>l_sae.sas</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>l_protdev.sas</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5918,17 +5918,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>L16.2.6</t>
+          <t>L16.2.4</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.6</t>
+          <t>Listing 16.2.4</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Listing of Concomitant Medications</t>
+          <t>Listing of Adverse Events</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>l_conmed.sas</t>
+          <t>l_ae.sas</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>WHO-DD 2024Q1</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -5981,17 +5981,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>L16.2.7</t>
+          <t>L16.2.5</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.7</t>
+          <t>Listing 16.2.5</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Listing of Laboratory Data — Hematology and Chemistry</t>
+          <t>Listing of Serious Adverse Events</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -6016,15 +6016,19 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADLB</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>l_lab.sas</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr"/>
+          <t>l_sae.sas</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6040,17 +6044,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>L16.2.8</t>
+          <t>L16.2.6</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.8</t>
+          <t>Listing 16.2.6</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Listing of Vital Signs</t>
+          <t>Listing of Concomitant Medications</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -6075,15 +6079,19 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADVS</t>
+          <t>ADSL, ADCM</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>l_vitalsigns.sas</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr"/>
+          <t>l_conmed.sas</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>WHO-DD [version]</t>
+        </is>
+      </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6099,17 +6107,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>L16.2.9</t>
+          <t>L16.2.7</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.9</t>
+          <t>Listing 16.2.7</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Listing of ECG Data</t>
+          <t>Listing of Laboratory Data — Hematology and Chemistry</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -6124,7 +6132,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Safety Population with ECG Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -6134,12 +6142,12 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADEG</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>l_ecg.sas</t>
+          <t>l_lab.sas</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr"/>
@@ -6158,17 +6166,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>L16.2.10</t>
+          <t>L16.2.8</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.10</t>
+          <t>Listing 16.2.8</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Listing of Tumor Response Data</t>
+          <t>Listing of Vital Signs</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -6183,22 +6191,22 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADVS</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>l_tumor_response.sas</t>
+          <t>l_vitalsigns.sas</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr"/>
@@ -6217,17 +6225,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>L16.2.11</t>
+          <t>L16.2.9</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.11</t>
+          <t>Listing 16.2.9</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Listing of Survival Data</t>
+          <t>Listing of ECG Data</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -6242,22 +6250,22 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>Safety Population with ECG Data</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADEG</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>l_survival.sas</t>
+          <t>l_ecg.sas</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr"/>
@@ -6276,17 +6284,17 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>L16.2.12</t>
+          <t>L16.2.10</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.12</t>
+          <t>Listing 16.2.10</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Listing of Study Drug Exposure and Dose Modifications</t>
+          <t>Listing of Tumor Response Data</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -6301,22 +6309,22 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADEX</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>l_exposure.sas</t>
+          <t>l_tumor_response.sas</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr"/>
@@ -6335,17 +6343,17 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>L16.2.13</t>
+          <t>L16.2.11</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.13</t>
+          <t>Listing 16.2.11</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Listing of Medical History Verbatim vs. Coded Terms</t>
+          <t>Listing of Survival Data</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -6360,29 +6368,25 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADMH</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>l_mh_coded.sas</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA 26.0</t>
-        </is>
-      </c>
+          <t>l_survival.sas</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6398,17 +6402,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>L16.2.14</t>
+          <t>L16.2.12</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.14</t>
+          <t>Listing 16.2.12</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Listing of PK Parameters by Subject</t>
+          <t>Listing of Study Drug Exposure and Dose Modifications</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -6423,7 +6427,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -6433,12 +6437,12 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPP</t>
+          <t>ADSL, ADEX</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>l_pk_params.sas</t>
+          <t>l_exposure.sas</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr"/>
@@ -6457,17 +6461,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>L16.2.15</t>
+          <t>L16.2.13</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.15</t>
+          <t>Listing 16.2.13</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Listing of ADA and Neutralizing Antibody Results</t>
+          <t>Listing of Medical History Verbatim vs. Coded Terms</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -6482,7 +6486,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -6492,15 +6496,19 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADMH</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>l_ada.sas</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr"/>
+          <t>l_mh_coded.sas</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6516,17 +6524,17 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>L16.2.16</t>
+          <t>L16.2.14</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.16</t>
+          <t>Listing 16.2.14</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+          <t>Listing of PK Concentrations by Subject and Timepoint</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -6541,22 +6549,22 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL, ADPC</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>l_subsequent_therapy.sas</t>
+          <t>l_pk_conc.sas</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr"/>
@@ -6575,17 +6583,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>L16.2.17</t>
+          <t>L16.2.15</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.17</t>
+          <t>Listing 16.2.15</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Listing of PRO Assessments by Subject and Visit</t>
+          <t>Listing of PK Parameters by Subject</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -6600,7 +6608,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>ITT with PRO Data</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -6610,12 +6618,12 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPRO</t>
+          <t>ADSL, ADPP</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>l_pro.sas</t>
+          <t>l_pk_params.sas</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr"/>
@@ -6631,8 +6639,362 @@
       </c>
       <c r="M101" s="4" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.16</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.16</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Listing of ADA and Neutralizing Antibody Results</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>l_ada.sas</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.17</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.17</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Biomarker Results by Subject and Visit</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>ITT with Biomarker Data</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADBM</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>l_biomarker.sas</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.18</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.18</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Listing of PRO Assessments by Subject and Visit</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>ITT with PRO Data</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>l_pro.sas</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.19</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.19</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>l_subsequent_therapy.sas</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr"/>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.20</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.20</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Deaths — All Subjects</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>All Randomized Subjects</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE, ADTTE</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>l_deaths.sas</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.21</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.21</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Prior and Subsequent Anti-Cancer Surgery/Radiotherapy</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Full Analysis Set</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>l_prior_cancer_proc.sas</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M101"/>
+  <autoFilter ref="A1:M107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -6786,11 +7148,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Continuous: n, Mean, SD, Median, Min, Max. Categorical: n (%).</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6899,7 +7257,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -6962,7 +7320,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>WHO-DD 2024Q1</t>
+          <t>WHO-DD [version]</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -7202,7 +7560,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -7265,7 +7623,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>WHO-DD 2024Q1</t>
+          <t>WHO-DD [version]</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -7352,7 +7710,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Summary of Study Drug Exposure</t>
+          <t>Summary of Study Drug Exposure — Duration, Cycles, Dose Intensity</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -7760,7 +8118,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ITT and Per-Protocol (PP) Populations</t>
+          <t>ITT and PP Populations</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8166,7 +8524,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Cumulative Distribution Function Plot</t>
+          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -8866,145 +9224,137 @@
       <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.4</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.4</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.20</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.20</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ITT Alive and On-Study at 6 Months</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADRS</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>f_waterfall.sas</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>t_landmark_os.sas</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.5</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.5</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.21</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.21</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Time to First Subsequent Therapy (TFST)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>ITT with Measurable Disease</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADRS</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>f_spider.sas</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE, ADCM</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>t_tfst.sas</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F14.2.6</t>
+          <t>F14.2.4</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.6</t>
+          <t>Figure 14.2.4</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Swimmer Plot — Duration of Treatment and Response</t>
+          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -9019,7 +9369,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -9029,12 +9379,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADEX, ADRS</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>f_swimmer.sas</t>
+          <t>f_waterfall.sas</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -9057,17 +9407,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>F14.2.7</t>
+          <t>F14.2.5</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.7</t>
+          <t>Figure 14.2.5</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
+          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -9082,7 +9432,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT with Measurable Disease</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -9092,12 +9442,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>f_km_pfs.sas</t>
+          <t>f_spider.sas</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
@@ -9120,17 +9470,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F14.2.8</t>
+          <t>F14.2.6</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.8</t>
+          <t>Figure 14.2.6</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Overall Survival</t>
+          <t>Swimmer Plot — Duration of Treatment and Response</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -9145,7 +9495,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -9155,12 +9505,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADEX, ADRS</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>f_km_os.sas</t>
+          <t>f_swimmer.sas</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -9183,17 +9533,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>F14.2.9</t>
+          <t>F14.2.7</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.9</t>
+          <t>Figure 14.2.7</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — PFS by Subgroup</t>
+          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -9223,7 +9573,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>f_forest_pfs.sas</t>
+          <t>f_km_pfs.sas</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -9246,17 +9596,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>F14.2.10</t>
+          <t>F14.2.8</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.10</t>
+          <t>Figure 14.2.8</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — OS by Subgroup</t>
+          <t>Kaplan-Meier Plot — Overall Survival</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -9286,7 +9636,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>f_forest_os.sas</t>
+          <t>f_km_os.sas</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
@@ -9307,122 +9657,130 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.20</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.20</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.9</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.9</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — PFS by Subgroup</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>ITT Alive and On-Study at 6 Months</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADTTE</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>t_landmark_os.sas</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_pfs.sas</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.21</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.21</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Exposure-Response Correlation</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.10</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.10</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — OS by Subgroup</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Evaluable Population</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPK, ADEFF</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>t_pkpd_corr.sas</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_os.sas</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -9437,7 +9795,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Time to First Subsequent Therapy (TFST)</t>
+          <t>PK/PD Exposure-Response Correlation Analysis</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -9452,22 +9810,22 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>PK/PD Evaluable Population</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE, ADCM</t>
+          <t>ADSL, ADPK, ADEFF</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>t_tfst.sas</t>
+          <t>t_pkpd_corr.sas</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -9629,7 +9987,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -9692,7 +10050,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -9720,7 +10078,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by SOC, PT, and Maximum CTCAE Grade (Treatment A)</t>
+          <t>TEAEs by SOC, PT, and Maximum CTCAE Grade (Group 1)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9755,7 +10113,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -9818,7 +10176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -9881,7 +10239,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -9944,7 +10302,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -10007,7 +10365,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -10035,7 +10393,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TEAEs Leading to Death (Grade 5)</t>
+          <t>Summary of Deaths</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -10060,19 +10418,15 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL, ADAE, ADTTE</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>l_ae_death.sas</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>t_deaths.sas</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -10133,7 +10487,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -10196,7 +10550,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -10259,7 +10613,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -10287,7 +10641,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by Age Group Subgroup (&gt;=5% in Any Arm)</t>
+          <t>TEAEs by Age Group Subgroup</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -10322,7 +10676,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -10350,7 +10704,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by Sex Subgroup (&gt;=5% in Any Arm)</t>
+          <t>TEAEs by Sex Subgroup</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -10385,7 +10739,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -10413,7 +10767,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Listing of All Deaths with Narrative Reference</t>
+          <t>Hy's Law Cases — Liver Chemistry Screening</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -10428,7 +10782,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>All Randomized Subjects</t>
+          <t>Safety Population with Baseline and Post-Baseline Labs</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10438,12 +10792,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADTTE</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>l_deaths.sas</t>
+          <t>t_hys_law.sas</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -10472,7 +10826,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Hy's Law Cases — Liver Chemistry Screening</t>
+          <t>Laboratory Parameters — Shift Table (Baseline to Worst Post-Baseline)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -10487,7 +10841,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with Baseline and Post-Baseline Labs</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10502,10 +10856,14 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>t_hys_law.sas</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+          <t>t_lab_shift.sas</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -10531,7 +10889,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Parameters — Shift Table (Baseline to Worst Post-Baseline)</t>
+          <t>Hematology Parameters — Summary Statistics by Visit</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -10561,14 +10919,10 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>t_lab_shift.sas</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>t_heme_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -10594,7 +10948,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Hematology Parameters — Summary Statistics by Visit</t>
+          <t>Clinical Chemistry Parameters — Summary Statistics by Visit</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -10624,7 +10978,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>t_heme_by_visit.sas</t>
+          <t>t_chem_by_visit.sas</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -10653,7 +11007,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Clinical Chemistry Parameters — Summary Statistics by Visit</t>
+          <t>Laboratory Abnormalities — Grade &gt;=3 Listing</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -10683,10 +11037,14 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>t_chem_by_visit.sas</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>l_lab_grade3.sas</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -10712,7 +11070,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Abnormalities — Grade &gt;=3 Listing</t>
+          <t>Laboratory Toxicity Grade Shift Over Time (by Cycle)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -10742,12 +11100,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>l_lab_grade3.sas</t>
+          <t>t_lab_shift_cycle.sas</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>CTCAE 5.0</t>
+          <t>CTCAE [xx]</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -10763,82 +11121,82 @@
       <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>T14.3.20</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.3.20</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Laboratory Toxicity Grade Shift Over Time (by Cycle)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>F14.3.1</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.3.1</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Mean (+/- SD) Change in Laboratory Parameters Over Time</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADLB</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>t_lab_shift_cycle.sas</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>CTCAE 5.0</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>f_lab_longitudinal.sas</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>F14.3.1</t>
+          <t>F14.3.2</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.3.1</t>
+          <t>Figure 14.3.2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Mean (+/- SD) Change in Laboratory Parameters Over Time</t>
+          <t>Box Plot — Liver Function Tests by Visit</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -10868,7 +11226,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>f_lab_longitudinal.sas</t>
+          <t>f_lft_box.sas</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -10889,67 +11247,63 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>F14.3.2</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.3.2</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Box Plot — Liver Function Tests by Visit</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.20</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.20</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Vital Signs — Summary Statistics by Visit</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADLB</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>f_lft_box.sas</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>t_vs_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -10964,7 +11318,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Vital Signs — Summary Statistics by Visit</t>
+          <t>Vital Signs — Clinically Notable Abnormalities by Visit</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -10994,7 +11348,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>t_vs_by_visit.sas</t>
+          <t>t_vs_notable.sas</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -11011,78 +11365,82 @@
       <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>T14.3.22</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.3.22</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Vital Signs — Clinically Notable Abnormalities by Visit</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>F14.3.3</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.3.3</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Mean (+/- SD) Vital Signs Over Time</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADVS</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>t_vs_notable.sas</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>f_vs_longitudinal.sas</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F14.3.3</t>
+          <t>F14.3.4</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.3.3</t>
+          <t>Figure 14.3.4</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Mean (+/- SD) Vital Signs Over Time</t>
+          <t>Liver Function Panel — Mean Over Time with ULN Reference</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -11107,12 +11465,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADVS</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>f_vs_longitudinal.sas</t>
+          <t>f_lft_uln.sas</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -11133,67 +11491,63 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>F14.3.4</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.3.4</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Liver Function Panel — Mean Over Time with ULN Reference</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.22</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.22</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ECG Parameters — Summary Statistics by Visit</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADLB</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>f_lft_uln.sas</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ECG Data</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADEG</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>t_ecg_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -11208,7 +11562,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ECG Parameters — Summary Statistics by Visit</t>
+          <t>ECG QTcF Categorical Analysis</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -11238,7 +11592,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>t_ecg_by_visit.sas</t>
+          <t>t_qtcf_cat.sas</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -11267,7 +11621,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ECG QTcF Categorical Analysis</t>
+          <t>ECG Qualitative Assessment — Shift Table</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -11297,7 +11651,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>t_qtcf_cat.sas</t>
+          <t>t_ecg_shift.sas</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -11326,7 +11680,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ECG Qualitative Assessment — Shift Table</t>
+          <t>Infusion-Related Reactions by Preferred Term</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -11341,7 +11695,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ECG Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11351,15 +11705,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEG</t>
+          <t>ADSL, ADAE, ADEX</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>t_ecg_shift.sas</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
+          <t>t_irr.sas</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -11385,7 +11743,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Infusion-Related Reactions by Preferred Term</t>
+          <t>ECOG Performance Status Shift Table</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -11410,19 +11768,15 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADEX</t>
+          <t>ADSL, ADQS</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>t_irr.sas</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
-        </is>
-      </c>
+          <t>t_ecog_shift.sas</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -11448,7 +11802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11605,7 +11959,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Summary of PK Parameters by Subject</t>
+          <t>Summary of Pharmacokinetic Parameters</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -11652,78 +12006,78 @@
       <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.1</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.1</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Pharmacokinetic Concentrations by Subject and Timepoint</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Anti-Drug Antibody (ADA) Incidence</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>l_pk_conc.sas</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>t_ada_incidence.sas</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>T14.4.3</t>
+          <t>T14.4.4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.3</t>
+          <t>Table 14.4.4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Immunogenicity Summary — Anti-Drug Antibody (ADA) Incidence</t>
+          <t>Summary of Biomarker Results by Visit</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -11738,7 +12092,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>ITT Population with Biomarker Data</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11748,12 +12102,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>t_ada_incidence.sas</t>
+          <t>t_biomarker_visit.sas</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -11770,78 +12124,78 @@
       <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.2</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.2</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Immunogenicity Results by Subject and Visit</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Patient-Reported Outcomes by Visit</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population with ADA Samples</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADIS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>l_immuno.sas</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population with PRO Data</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>t_pro_summary.sas</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>T14.4.4</t>
+          <t>T14.4.6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.4</t>
+          <t>Table 14.4.6</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Summary of Biomarker Results by Visit</t>
+          <t>Summary of Pharmacodynamics — Soluble Biomarkers by Visit</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -11856,7 +12210,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ITT Population with Biomarker Data</t>
+          <t>PD Population</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11866,12 +12220,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, ADPD</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>t_biomarker_visit.sas</t>
+          <t>t_pd_summary.sas</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -11888,184 +12242,318 @@
       <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.3</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.3</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Biomarker Results by Subject and Visit</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Central Molecular Test Results and Gene Aberrations at Baseline</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>ITT with Biomarker Data</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Full Analysis Set</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>ADSL, ADBM</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>l_biomarker.sas</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>t_gene_aberrations.sas</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.5</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.5</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Summary of Patient-Reported Outcomes by Visit</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.1</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.1</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>ITT Population with PRO Data</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPRO</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>t_pro_summary.sas</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_profile.sas</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>L14.4.4</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Listing 14.4.4</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Patient-Reported Outcomes by Subject and Visit</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.2</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Overlaying Individual PK Concentration Profiles</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>ITT with PRO Data</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADPRO</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>l_pro.sas</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_overlay.sas</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.3</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.3</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>PD Population</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPD</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>f_pd_time.sas</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.4</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.4</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Boxplot of Biomarkers at Baseline vs. Response Status</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Full Analysis Set with Biomarker Data</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADBM</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>f_biomarker_box.sas</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -12077,7 +12565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12190,7 +12678,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>All Randomized Subjects</t>
+          <t>All Screened Subjects</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -12308,7 +12796,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>All Randomized Subjects</t>
+          <t>All Enrolled Subjects</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -12387,7 +12875,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -12450,7 +12938,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>MedDRA 26.0; CTCAE 5.0</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -12513,7 +13001,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>WHO-DD 2024Q1</t>
+          <t>WHO-DD [version]</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -12930,7 +13418,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>MedDRA 26.0</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -12958,7 +13446,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Listing of PK Parameters by Subject</t>
+          <t>Listing of PK Concentrations by Subject and Timepoint</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -12983,12 +13471,12 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPP</t>
+          <t>ADSL, ADPC</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>l_pk_params.sas</t>
+          <t>l_pk_conc.sas</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
@@ -13017,7 +13505,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Listing of ADA and Neutralizing Antibody Results</t>
+          <t>Listing of PK Parameters by Subject</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -13032,7 +13520,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -13042,12 +13530,12 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADPP</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>l_ada.sas</t>
+          <t>l_pk_params.sas</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
@@ -13076,7 +13564,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+          <t>Listing of ADA and Neutralizing Antibody Results</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -13091,22 +13579,22 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>Safety Population with ADA Samples</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL, ADIS</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>l_subsequent_therapy.sas</t>
+          <t>l_ada.sas</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
@@ -13135,7 +13623,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Listing of PRO Assessments by Subject and Visit</t>
+          <t>Listing of Biomarker Results by Subject and Visit</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -13150,7 +13638,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>ITT with PRO Data</t>
+          <t>ITT with Biomarker Data</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -13160,12 +13648,12 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPRO</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>l_pro.sas</t>
+          <t>l_biomarker.sas</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
@@ -13181,8 +13669,244 @@
       </c>
       <c r="M18" s="4" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.18</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.18</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Listing of PRO Assessments by Subject and Visit</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>ITT with PRO Data</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>l_pro.sas</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.19</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.19</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>l_subsequent_therapy.sas</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.20</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Deaths — All Subjects</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>All Randomized Subjects</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE, ADTTE</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>l_deaths.sas</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.21</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Prior and Subsequent Anti-Cancer Surgery/Radiotherapy</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Full Analysis Set</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>l_prior_cancer_proc.sas</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -13402,7 +14126,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>First column preserved; adaptive placeholders such as XX or xx (xx.x) are used by shell style</t>
+          <t>First column preserved; non-structural cells use style-appropriate shell placeholders such as XX or xx (xx.x)</t>
         </is>
       </c>
     </row>
@@ -13436,7 +14160,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Generated figure retained as simulated image</t>
+          <t>Simulated figure retained; shell family or study-specific notes if needed</t>
         </is>
       </c>
     </row>
@@ -13492,7 +14216,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>The workbook covers CSR Sections 14.1, 14.2, 14.3, 14.4, and 16.2 only.</t>
+          <t>The workbook covers CSR Sections 14.1, 14.2, 14.3, 14.4, and 16.2 only; Section 16.1 is out of scope for this generator.</t>
         </is>
       </c>
     </row>
@@ -13504,7 +14228,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Use the Applicability column to identify shells relevant to oncology, non-oncology, or both.</t>
+          <t>Use the Applicability column to identify shells relevant to oncology, non-oncology, or both. These labels guide study-specific shell selection rather than serving as workflow status flags.</t>
         </is>
       </c>
     </row>

--- a/output/TFL_TOC_v2.1.0.xlsx
+++ b/output/TFL_TOC_v2.1.0.xlsx
@@ -18,10 +18,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOC_Master'!$A$1:$M$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOC_Master'!$A$1:$M$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'14.1_Demographics'!$A$1:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'14.2_Efficacy'!$A$1:$M$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'14.3_Safety'!$A$1:$M$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'14.3_Safety'!$A$1:$M$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'14.4_Special'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'16.2_Listings'!$A$1:$M$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Field_Definitions'!$A$1:$C$14</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEFF</t>
+          <t>ADSL, ADEFF, ADTTE</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -5076,17 +5076,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>T14.4.1</t>
+          <t>T14.3.27</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.1</t>
+          <t>Table 14.3.27</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Summary of Pharmacokinetic Concentrations by Timepoint</t>
+          <t>Adverse Events of Special Interest (AESI) — Summary</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -5111,15 +5111,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPC</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>t_pk_conc.sas</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
+          <t>t_aesi_summary.sas</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5135,17 +5139,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>T14.4.2</t>
+          <t>T14.3.28</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.2</t>
+          <t>Table 14.3.28</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Summary of Pharmacokinetic Parameters</t>
+          <t>AESI — Time to First Occurrence</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5155,12 +5159,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -5170,15 +5174,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPP</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>t_pk_params.sas</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr"/>
+          <t>t_aesi_ttf.sas</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5194,17 +5202,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>T14.4.3</t>
+          <t>T14.3.29</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.3</t>
+          <t>Table 14.3.29</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Summary of Anti-Drug Antibody (ADA) Incidence</t>
+          <t>Laboratory Parameters — Descriptive Statistics and Change from Baseline by Visit</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5214,12 +5222,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -5229,15 +5237,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>t_ada_incidence.sas</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr"/>
+          <t>t_lab_chg_bl.sas</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5253,17 +5265,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>T14.4.4</t>
+          <t>T14.3.30</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.4</t>
+          <t>Table 14.3.30</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Summary of Biomarker Results by Visit</t>
+          <t>Laboratory Parameters — CTCAE Grade Shift (Baseline to Worst Post-Baseline)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5273,12 +5285,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>ITT Population with Biomarker Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -5288,15 +5300,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>t_biomarker_visit.sas</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr"/>
+          <t>t_lab_grade_shift.sas</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5312,17 +5328,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>T14.4.5</t>
+          <t>T14.4.1</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.5</t>
+          <t>Table 14.4.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Summary of Patient-Reported Outcomes by Visit</t>
+          <t>Summary of Pharmacokinetic Concentrations by Timepoint</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5337,7 +5353,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>ITT Population with PRO Data</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -5347,12 +5363,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPRO</t>
+          <t>ADSL, ADPC</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>t_pro_summary.sas</t>
+          <t>t_pk_conc.sas</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -5371,17 +5387,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>T14.4.6</t>
+          <t>T14.4.2</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.6</t>
+          <t>Table 14.4.2</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Summary of Pharmacodynamics — Soluble Biomarkers by Visit</t>
+          <t>Summary of Pharmacokinetic Parameters</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5396,7 +5412,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>PD Population</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -5406,12 +5422,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPD</t>
+          <t>ADSL, ADPP</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>t_pd_summary.sas</t>
+          <t>t_pk_params.sas</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -5430,17 +5446,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>T14.4.7</t>
+          <t>T14.4.3</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.7</t>
+          <t>Table 14.4.3</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Summary of Central Molecular Test Results and Gene Aberrations at Baseline</t>
+          <t>Summary of Anti-Drug Antibody (ADA) Incidence</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5455,22 +5471,22 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Full Analysis Set</t>
+          <t>Safety Population with ADA Samples</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, ADIS</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>t_gene_aberrations.sas</t>
+          <t>t_ada_incidence.sas</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -5487,511 +5503,507 @@
       <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.4</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.4</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Biomarker Results by Visit</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population with Biomarker Data</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADBM</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>t_biomarker_visit.sas</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.5</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.5</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Patient-Reported Outcomes by Visit</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population with PRO Data</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>t_pro_summary.sas</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.6</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.6</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Pharmacodynamics — Soluble Biomarkers by Visit</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>PD Population</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPD</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>t_pd_summary.sas</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.7</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.7</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Central Molecular Test Results and Gene Aberrations at Baseline</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Full Analysis Set</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADBM</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>t_gene_aberrations.sas</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>F14.4.1</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.1</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>PK Population</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADPC</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr">
         <is>
           <t>f_pk_profile.sas</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr"/>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>F14.4.2</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.2</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Overlaying Individual PK Concentration Profiles</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>PK Population</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADPC</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr">
         <is>
           <t>f_pk_overlay.sas</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr"/>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>F14.4.3</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.3</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>PD Population</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADPD</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>f_pd_time.sas</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr"/>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="inlineStr">
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>F14.4.4</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.4</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Boxplot of Biomarkers at Baseline vs. Response Status</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>Full Analysis Set with Biomarker Data</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADBM</t>
         </is>
       </c>
-      <c r="I86" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>f_biomarker_box.sas</t>
         </is>
       </c>
-      <c r="J86" s="3" t="inlineStr"/>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.1</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.1</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Subject Disposition</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>All Screened Subjects</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>l_disposition.sas</t>
-        </is>
-      </c>
-      <c r="J87" s="4" t="inlineStr"/>
-      <c r="K87" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M87" s="4" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.2</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.2</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Demographic Data</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>All Randomized Subjects</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>l_demog.sas</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr"/>
-      <c r="K88" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.3</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.3</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Protocol Deviations</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>All Enrolled Subjects</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, DV</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>l_protdev.sas</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr"/>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.4</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.4</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Adverse Events</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADAE</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t>l_ae.sas</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>L16.2.5</t>
+          <t>L16.2.1</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.5</t>
+          <t>Listing 16.2.1</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Listing of Serious Adverse Events</t>
+          <t>Listing of Subject Disposition</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -6006,7 +6018,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>All Screened Subjects</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -6016,19 +6028,15 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>l_sae.sas</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
-        </is>
-      </c>
+          <t>l_disposition.sas</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6044,17 +6052,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>L16.2.6</t>
+          <t>L16.2.2</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.6</t>
+          <t>Listing 16.2.2</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Listing of Concomitant Medications</t>
+          <t>Listing of Demographic Data</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -6069,7 +6077,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>All Randomized Subjects</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -6079,19 +6087,15 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>l_conmed.sas</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>WHO-DD [version]</t>
-        </is>
-      </c>
+          <t>l_demog.sas</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6107,17 +6111,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>L16.2.7</t>
+          <t>L16.2.3</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.7</t>
+          <t>Listing 16.2.3</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Listing of Laboratory Data — Hematology and Chemistry</t>
+          <t>Listing of Protocol Deviations</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -6132,7 +6136,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>All Enrolled Subjects</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -6142,12 +6146,12 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADLB</t>
+          <t>ADSL, DV</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>l_lab.sas</t>
+          <t>l_protdev.sas</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr"/>
@@ -6166,17 +6170,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>L16.2.8</t>
+          <t>L16.2.4</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.8</t>
+          <t>Listing 16.2.4</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Listing of Vital Signs</t>
+          <t>Listing of Adverse Events</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -6201,15 +6205,19 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADVS</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>l_vitalsigns.sas</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr"/>
+          <t>l_ae.sas</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6225,17 +6233,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>L16.2.9</t>
+          <t>L16.2.5</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.9</t>
+          <t>Listing 16.2.5</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Listing of ECG Data</t>
+          <t>Listing of Serious Adverse Events</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -6250,7 +6258,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Safety Population with ECG Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -6260,15 +6268,19 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADEG</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>l_ecg.sas</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr"/>
+          <t>l_sae.sas</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6284,17 +6296,17 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>L16.2.10</t>
+          <t>L16.2.6</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.10</t>
+          <t>Listing 16.2.6</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Listing of Tumor Response Data</t>
+          <t>Listing of Concomitant Medications</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -6309,25 +6321,29 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADCM</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>l_tumor_response.sas</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr"/>
+          <t>l_conmed.sas</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>WHO-DD [version]</t>
+        </is>
+      </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6343,17 +6359,17 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>L16.2.11</t>
+          <t>L16.2.7</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.11</t>
+          <t>Listing 16.2.7</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Listing of Survival Data</t>
+          <t>Listing of Laboratory Data — Hematology and Chemistry</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -6368,22 +6384,22 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>l_survival.sas</t>
+          <t>l_lab.sas</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr"/>
@@ -6402,17 +6418,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>L16.2.12</t>
+          <t>L16.2.8</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.12</t>
+          <t>Listing 16.2.8</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Listing of Study Drug Exposure and Dose Modifications</t>
+          <t>Listing of Vital Signs</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -6437,12 +6453,12 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADEX</t>
+          <t>ADSL, ADVS</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>l_exposure.sas</t>
+          <t>l_vitalsigns.sas</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr"/>
@@ -6461,17 +6477,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>L16.2.13</t>
+          <t>L16.2.9</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.13</t>
+          <t>Listing 16.2.9</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Listing of Medical History Verbatim vs. Coded Terms</t>
+          <t>Listing of ECG Data</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -6486,7 +6502,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>Safety Population with ECG Data</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -6496,19 +6512,15 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADMH</t>
+          <t>ADSL, ADEG</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>l_mh_coded.sas</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]</t>
-        </is>
-      </c>
+          <t>l_ecg.sas</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6524,17 +6536,17 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>L16.2.14</t>
+          <t>L16.2.10</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.14</t>
+          <t>Listing 16.2.10</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Listing of PK Concentrations by Subject and Timepoint</t>
+          <t>Listing of Tumor Response Data</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -6549,22 +6561,22 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPC</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>l_pk_conc.sas</t>
+          <t>l_tumor_response.sas</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr"/>
@@ -6583,17 +6595,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>L16.2.15</t>
+          <t>L16.2.11</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.15</t>
+          <t>Listing 16.2.11</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Listing of PK Parameters by Subject</t>
+          <t>Listing of Survival Data</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -6608,22 +6620,22 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPP</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>l_pk_params.sas</t>
+          <t>l_survival.sas</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr"/>
@@ -6642,17 +6654,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>L16.2.16</t>
+          <t>L16.2.12</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.16</t>
+          <t>Listing 16.2.12</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Listing of ADA and Neutralizing Antibody Results</t>
+          <t>Listing of Study Drug Exposure and Dose Modifications</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -6667,7 +6679,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -6677,12 +6689,12 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADEX</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>l_ada.sas</t>
+          <t>l_exposure.sas</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr"/>
@@ -6701,17 +6713,17 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>L16.2.17</t>
+          <t>L16.2.13</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.17</t>
+          <t>Listing 16.2.13</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Listing of Biomarker Results by Subject and Visit</t>
+          <t>Listing of Medical History Verbatim vs. Coded Terms</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -6726,7 +6738,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>ITT with Biomarker Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -6736,15 +6748,19 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, ADMH</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>l_biomarker.sas</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr"/>
+          <t>l_mh_coded.sas</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -6760,17 +6776,17 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>L16.2.18</t>
+          <t>L16.2.14</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.18</t>
+          <t>Listing 16.2.14</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Listing of PRO Assessments by Subject and Visit</t>
+          <t>Listing of PK Concentrations by Subject and Timepoint</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -6785,7 +6801,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>ITT with PRO Data</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -6795,12 +6811,12 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPRO</t>
+          <t>ADSL, ADPC</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>l_pro.sas</t>
+          <t>l_pk_conc.sas</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr"/>
@@ -6819,17 +6835,17 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>L16.2.19</t>
+          <t>L16.2.15</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.19</t>
+          <t>Listing 16.2.15</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+          <t>Listing of PK Parameters by Subject</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -6844,22 +6860,22 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL, ADPP</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>l_subsequent_therapy.sas</t>
+          <t>l_pk_params.sas</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr"/>
@@ -6878,17 +6894,17 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>L16.2.20</t>
+          <t>L16.2.16</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.20</t>
+          <t>Listing 16.2.16</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Listing of Deaths — All Subjects</t>
+          <t>Listing of ADA and Neutralizing Antibody Results</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6903,7 +6919,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>All Randomized Subjects</t>
+          <t>Safety Population with ADA Samples</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6913,12 +6929,12 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADTTE</t>
+          <t>ADSL, ADIS</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>l_deaths.sas</t>
+          <t>l_ada.sas</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr"/>
@@ -6937,17 +6953,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>L16.2.21</t>
+          <t>L16.2.17</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.21</t>
+          <t>Listing 16.2.17</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Listing of Prior and Subsequent Anti-Cancer Surgery/Radiotherapy</t>
+          <t>Listing of Biomarker Results by Subject and Visit</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6962,22 +6978,22 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Full Analysis Set</t>
+          <t>ITT with Biomarker Data</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>l_prior_cancer_proc.sas</t>
+          <t>l_biomarker.sas</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr"/>
@@ -6993,8 +7009,244 @@
       </c>
       <c r="M107" s="4" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.18</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.18</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Listing of PRO Assessments by Subject and Visit</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>ITT with PRO Data</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>l_pro.sas</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.19</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.19</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>l_subsequent_therapy.sas</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.20</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.20</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Deaths — All Subjects</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>All Randomized Subjects</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE, ADTTE</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>l_deaths.sas</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.21</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.21</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Prior and Subsequent Anti-Cancer Surgery/Radiotherapy</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Full Analysis Set</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>l_prior_cancer_proc.sas</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M111" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M107"/>
+  <autoFilter ref="A1:M111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -8010,7 +8262,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEFF</t>
+          <t>ADSL, ADEFF, ADTTE</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -9854,7 +10106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11789,8 +12041,260 @@
       </c>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.27</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.27</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Adverse Events of Special Interest (AESI) — Summary</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>t_aesi_summary.sas</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.28</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.28</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>AESI — Time to First Occurrence</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>t_aesi_ttf.sas</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.29</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.29</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Parameters — Descriptive Statistics and Change from Baseline by Visit</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>t_lab_chg_bl.sas</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.30</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.30</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Parameters — CTCAE Grade Shift (Baseline to Worst Post-Baseline)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>t_lab_grade_shift.sas</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M31"/>
+  <autoFilter ref="A1:M35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/output/TFL_TOC_v2.1.0.xlsx
+++ b/output/TFL_TOC_v2.1.0.xlsx
@@ -18,10 +18,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOC_Master'!$A$1:$M$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'14.1_Demographics'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOC_Master'!$A$1:$M$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'14.1_Demographics'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'14.2_Efficacy'!$A$1:$M$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'14.3_Safety'!$A$1:$M$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'14.3_Safety'!$A$1:$M$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'14.4_Special'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'16.2_Listings'!$A$1:$M$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Field_Definitions'!$A$1:$C$14</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COVID-19 Medical History, Vaccination, and Testing Status</t>
+          <t>Summary of Study Drug Exposure — Duration, Cycles, Dose Intensity</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADMH</t>
+          <t>ADEX</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>t_covid19_status.sas</t>
+          <t>t_exposure_summary.sas</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Summary of Study Drug Exposure — Duration, Cycles, Dose Intensity</t>
+          <t>Summary of Genomic/Biomarker Baseline Characteristics</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1205,22 +1205,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT Population with Biomarker Data</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>ADEX</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>t_exposure_summary.sas</t>
+          <t>t_biomarker_baseline.sas</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1239,17 +1239,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>T14.1.12</t>
+          <t>T14.2.1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Table 14.1.12</t>
+          <t>Table 14.2.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Summary of Genomic/Biomarker Baseline Characteristics</t>
+          <t>Primary Efficacy Endpoint — Primary Analysis</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1259,27 +1259,27 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ITT Population with Biomarker Data</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, ADEFF</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>t_biomarker_baseline.sas</t>
+          <t>t_primary_eff.sas</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1298,17 +1298,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T14.2.1</t>
+          <t>T14.2.2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.1</t>
+          <t>Table 14.2.2</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Primary Efficacy Endpoint — Primary Analysis</t>
+          <t>Secondary Efficacy Endpoints — Summary</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEFF</t>
+          <t>ADSL, ADEFF, ADTTE</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>t_primary_eff.sas</t>
+          <t>t_secondary_eff.sas</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1357,17 +1357,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T14.2.2</t>
+          <t>T14.2.3</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.2</t>
+          <t>Table 14.2.3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Secondary Efficacy Endpoints — Summary</t>
+          <t>Subgroup Analysis of Primary Endpoint</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEFF, ADTTE</t>
+          <t>ADSL, ADEFF</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>t_secondary_eff.sas</t>
+          <t>t_subgroup_primary.sas</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1416,17 +1416,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T14.2.3</t>
+          <t>T14.2.4</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.3</t>
+          <t>Table 14.2.4</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Subgroup Analysis of Primary Endpoint</t>
+          <t>Sensitivity Analysis of Primary Endpoint</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT and PP Populations</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>t_subgroup_primary.sas</t>
+          <t>t_sensitivity_eff.sas</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1475,17 +1475,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T14.2.4</t>
+          <t>T14.2.5</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.4</t>
+          <t>Table 14.2.5</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Sensitivity Analysis of Primary Endpoint</t>
+          <t>Non-Inferiority Analysis of Primary Endpoint</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>ITT and PP Populations</t>
+          <t>Per-Protocol (PP) Population</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>t_sensitivity_eff.sas</t>
+          <t>t_ni_analysis.sas</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1534,17 +1534,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T14.2.5</t>
+          <t>T14.2.6</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.5</t>
+          <t>Table 14.2.6</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Non-Inferiority Analysis of Primary Endpoint</t>
+          <t>Tipping Point Analysis for Primary Endpoint</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Per-Protocol (PP) Population</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>t_ni_analysis.sas</t>
+          <t>t_tipping_point.sas</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1593,17 +1593,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>T14.2.6</t>
+          <t>T14.2.7</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.6</t>
+          <t>Table 14.2.7</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tipping Point Analysis for Primary Endpoint</t>
+          <t>Sensitivity Analysis by Estimand Strategy</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>t_tipping_point.sas</t>
+          <t>t_estimand_sens.sas</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1652,17 +1652,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>T14.2.7</t>
+          <t>T14.2.8</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.7</t>
+          <t>Table 14.2.8</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Sensitivity Analysis by Estimand Strategy</t>
+          <t>Time to Deterioration (TTD) — Quality of Life</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>ITT Population with PRO Data</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEFF</t>
+          <t>ADSL, ADPRO</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>t_estimand_sens.sas</t>
+          <t>t_ttd_qol.sas</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1709,78 +1709,82 @@
       <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.8</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.8</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Time to Deterioration (TTD) — Quality of Life</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.1</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.1</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — Primary Endpoint by Subgroup</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>ITT Population with PRO Data</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPRO</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>t_ttd_qol.sas</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADEFF</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_primary.sas</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>F14.2.1</t>
+          <t>F14.2.2</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.1</t>
+          <t>Figure 14.2.2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — Primary Endpoint by Subgroup</t>
+          <t>Longitudinal Plot — Primary Endpoint Over Time</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1810,7 +1814,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>f_forest_primary.sas</t>
+          <t>f_longitudinal_eff.sas</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -1833,17 +1837,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>F14.2.2</t>
+          <t>F14.2.3</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.2</t>
+          <t>Figure 14.2.3</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal Plot — Primary Endpoint Over Time</t>
+          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1873,7 +1877,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>f_longitudinal_eff.sas</t>
+          <t>f_cdf_eff.sas</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -1894,82 +1898,78 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.3</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.3</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.9</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.9</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Tumor Response — Best Overall Response (BOR)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADEFF</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>f_cdf_eff.sas</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>t_bor.sas</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>T14.2.9</t>
+          <t>T14.2.10</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.9</t>
+          <t>Table 14.2.10</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Best Overall Response (BOR)</t>
+          <t>Tumor Response — Objective Response Rate (ORR)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>t_bor.sas</t>
+          <t>t_orr.sas</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -2018,17 +2018,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>T14.2.10</t>
+          <t>T14.2.11</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.10</t>
+          <t>Table 14.2.11</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Objective Response Rate (ORR)</t>
+          <t>Tumor Response — Disease Control Rate (DCR)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>t_orr.sas</t>
+          <t>t_dcr.sas</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -2077,17 +2077,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>T14.2.11</t>
+          <t>T14.2.12</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.11</t>
+          <t>Table 14.2.12</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Disease Control Rate (DCR)</t>
+          <t>Tumor Response — Duration of Response (DOR)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Responders (Confirmed CR or PR)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADRS, ADTTE</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>t_dcr.sas</t>
+          <t>t_dor.sas</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -2136,17 +2136,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>T14.2.12</t>
+          <t>T14.2.13</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.12</t>
+          <t>Table 14.2.13</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Duration of Response (DOR)</t>
+          <t>Tumor Response — Time to Response (TTR)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS, ADTTE</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>t_dor.sas</t>
+          <t>t_ttr.sas</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -2195,17 +2195,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>T14.2.13</t>
+          <t>T14.2.14</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.13</t>
+          <t>Table 14.2.14</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Time to Response (TTR)</t>
+          <t>Progression-Free Survival (PFS) — Primary Analysis</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Responders (Confirmed CR or PR)</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>t_ttr.sas</t>
+          <t>t_pfs_primary.sas</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2254,17 +2254,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>T14.2.14</t>
+          <t>T14.2.15</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.14</t>
+          <t>Table 14.2.15</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Progression-Free Survival (PFS) — Primary Analysis</t>
+          <t>Overall Survival (OS) — Primary Analysis</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_primary.sas</t>
+          <t>t_os_primary.sas</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2313,17 +2313,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>T14.2.15</t>
+          <t>T14.2.16</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.15</t>
+          <t>Table 14.2.16</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Overall Survival (OS) — Primary Analysis</t>
+          <t>PFS — Sensitivity Analysis</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>t_os_primary.sas</t>
+          <t>t_pfs_sensitivity.sas</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2372,17 +2372,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>T14.2.16</t>
+          <t>T14.2.17</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.16</t>
+          <t>Table 14.2.17</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PFS — Sensitivity Analysis</t>
+          <t>PFS — Subgroup Analysis</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_sensitivity.sas</t>
+          <t>t_pfs_subgroup.sas</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2431,17 +2431,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>T14.2.17</t>
+          <t>T14.2.18</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.17</t>
+          <t>Table 14.2.18</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>PFS — Subgroup Analysis</t>
+          <t>OS — Subgroup Analysis</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_subgroup.sas</t>
+          <t>t_os_subgroup.sas</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -2490,17 +2490,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>T14.2.18</t>
+          <t>T14.2.19</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.18</t>
+          <t>Table 14.2.19</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>OS — Subgroup Analysis</t>
+          <t>Summary of Target Lesion Changes from Baseline</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>t_os_subgroup.sas</t>
+          <t>t_target_lesion.sas</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2549,17 +2549,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>T14.2.19</t>
+          <t>T14.2.20</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.19</t>
+          <t>Table 14.2.20</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Summary of Target Lesion Changes from Baseline</t>
+          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
+          <t>ITT Alive and On-Study at 6 Months</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>t_target_lesion.sas</t>
+          <t>t_landmark_os.sas</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -2608,17 +2608,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>T14.2.20</t>
+          <t>T14.2.21</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.20</t>
+          <t>Table 14.2.21</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
+          <t>Time to First Subsequent Therapy (TFST)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>ITT Alive and On-Study at 6 Months</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADTTE, ADCM</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>t_landmark_os.sas</t>
+          <t>t_tfst.sas</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2665,78 +2665,82 @@
       <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.21</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.21</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Time to First Subsequent Therapy (TFST)</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.4</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.4</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>ITT Population</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADTTE, ADCM</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>t_tfst.sas</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>f_waterfall.sas</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>F14.2.4</t>
+          <t>F14.2.5</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.4</t>
+          <t>Figure 14.2.5</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
+          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2751,7 +2755,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
+          <t>ITT with Measurable Disease</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2766,7 +2770,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>f_waterfall.sas</t>
+          <t>f_spider.sas</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
@@ -2789,17 +2793,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>F14.2.5</t>
+          <t>F14.2.6</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.5</t>
+          <t>Figure 14.2.6</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
+          <t>Swimmer Plot — Duration of Treatment and Response</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2814,7 +2818,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2824,12 +2828,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADEX, ADRS</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>f_spider.sas</t>
+          <t>f_swimmer.sas</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -2852,17 +2856,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>F14.2.6</t>
+          <t>F14.2.7</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.6</t>
+          <t>Figure 14.2.7</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Swimmer Plot — Duration of Treatment and Response</t>
+          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -2877,7 +2881,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2887,12 +2891,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADEX, ADRS</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>f_swimmer.sas</t>
+          <t>f_km_pfs.sas</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
@@ -2915,17 +2919,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>F14.2.7</t>
+          <t>F14.2.8</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.7</t>
+          <t>Figure 14.2.8</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
+          <t>Kaplan-Meier Plot — Overall Survival</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2955,7 +2959,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>f_km_pfs.sas</t>
+          <t>f_km_os.sas</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -2978,17 +2982,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>F14.2.8</t>
+          <t>F14.2.9</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.8</t>
+          <t>Figure 14.2.9</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Overall Survival</t>
+          <t>Forest Plot — PFS by Subgroup</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3018,7 +3022,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>f_km_os.sas</t>
+          <t>f_forest_pfs.sas</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr"/>
@@ -3041,17 +3045,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>F14.2.9</t>
+          <t>F14.2.10</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.9</t>
+          <t>Figure 14.2.10</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — PFS by Subgroup</t>
+          <t>Forest Plot — OS by Subgroup</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3081,7 +3085,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>f_forest_pfs.sas</t>
+          <t>f_forest_os.sas</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -3102,82 +3106,78 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.10</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.10</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Forest Plot — OS by Subgroup</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.22</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.22</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>PK/PD Exposure-Response Correlation Analysis</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Intent-to-Treat (ITT) Population</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADTTE</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>f_forest_os.sas</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>PK/PD Evaluable Population</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPK, ADEFF</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>t_pkpd_corr.sas</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>T14.2.22</t>
+          <t>T14.3.1</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.22</t>
+          <t>Table 14.3.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>PK/PD Exposure-Response Correlation Analysis</t>
+          <t>Overall Summary of Treatment-Emergent Adverse Events</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>PK/PD Evaluable Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3202,15 +3202,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPK, ADEFF</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>t_pkpd_corr.sas</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
+          <t>t_ae_overview.sas</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -3226,17 +3230,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>T14.3.1</t>
+          <t>T14.3.2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.1</t>
+          <t>Table 14.3.2</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Overall Summary of Treatment-Emergent Adverse Events</t>
+          <t>TEAEs by System Organ Class and Preferred Term (&gt;=5% in Any Arm)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3266,7 +3270,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>t_ae_overview.sas</t>
+          <t>t_ae_soc_pt.sas</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3289,17 +3293,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>T14.3.2</t>
+          <t>T14.3.3</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.2</t>
+          <t>Table 14.3.3</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by System Organ Class and Preferred Term (&gt;=5% in Any Arm)</t>
+          <t>TEAEs by SOC, PT, and Maximum CTCAE Grade (Group 1)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3329,7 +3333,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>t_ae_soc_pt.sas</t>
+          <t>t_ae_grade.sas</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3352,17 +3356,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>T14.3.3</t>
+          <t>T14.3.4</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.3</t>
+          <t>Table 14.3.4</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by SOC, PT, and Maximum CTCAE Grade (Group 1)</t>
+          <t>Drug-Related TEAEs by SOC, PT, and Relationship</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3392,12 +3396,12 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>t_ae_grade.sas</t>
+          <t>t_ae_related.sas</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3415,17 +3419,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>T14.3.4</t>
+          <t>T14.3.5</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.4</t>
+          <t>Table 14.3.5</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Drug-Related TEAEs by SOC, PT, and Relationship</t>
+          <t>Serious Adverse Events by SOC and PT</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3455,7 +3459,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>t_ae_related.sas</t>
+          <t>t_sae_soc_pt.sas</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3478,17 +3482,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>T14.3.5</t>
+          <t>T14.3.6</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.5</t>
+          <t>Table 14.3.6</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Serious Adverse Events by SOC and PT</t>
+          <t>TEAEs Leading to Treatment Discontinuation by SOC and PT</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3518,7 +3522,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>t_sae_soc_pt.sas</t>
+          <t>t_ae_disc.sas</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,17 +3545,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>T14.3.6</t>
+          <t>T14.3.7</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.6</t>
+          <t>Table 14.3.7</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>TEAEs Leading to Treatment Discontinuation by SOC and PT</t>
+          <t>TEAEs Leading to Dose Reduction or Interruption by SOC and PT</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3581,7 +3585,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>t_ae_disc.sas</t>
+          <t>t_ae_dose_mod.sas</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3604,17 +3608,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>T14.3.7</t>
+          <t>T14.3.8</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.7</t>
+          <t>Table 14.3.8</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>TEAEs Leading to Dose Reduction or Interruption by SOC and PT</t>
+          <t>Summary of Deaths</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3639,19 +3643,15 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL, ADAE, ADTTE</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>t_ae_dose_mod.sas</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]</t>
-        </is>
-      </c>
+          <t>t_deaths.sas</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -3667,17 +3667,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>T14.3.8</t>
+          <t>T14.3.9</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.8</t>
+          <t>Table 14.3.9</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Summary of Deaths</t>
+          <t>TEAEs Occurring in &gt;=5% of Subjects by PT</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3702,15 +3702,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADTTE</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>t_deaths.sas</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr"/>
+          <t>t_ae_5pct.sas</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -3726,17 +3730,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>T14.3.9</t>
+          <t>T14.3.10</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.9</t>
+          <t>Table 14.3.10</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>TEAEs Occurring in &gt;=5% of Subjects by PT</t>
+          <t>TEAEs by Cycle / Treatment Period</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3761,17 +3765,17 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL, ADAE, ADEX</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>t_ae_5pct.sas</t>
+          <t>t_ae_by_cycle.sas</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>MedDRA [xx.x]</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3789,17 +3793,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>T14.3.10</t>
+          <t>T14.3.11</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.10</t>
+          <t>Table 14.3.11</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by Cycle / Treatment Period</t>
+          <t>Exposure-Adjusted TEAE Incidence Rates (per 100 Patient-Years)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3829,12 +3833,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>t_ae_by_cycle.sas</t>
+          <t>t_ae_adj_rate.sas</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+          <t>MedDRA [xx.x]</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3852,17 +3856,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>T14.3.11</t>
+          <t>T14.3.12</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.11</t>
+          <t>Table 14.3.12</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Exposure-Adjusted TEAE Incidence Rates (per 100 Patient-Years)</t>
+          <t>TEAEs by Age Group Subgroup</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3887,12 +3891,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADEX</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>t_ae_adj_rate.sas</t>
+          <t>t_ae_age.sas</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3915,17 +3919,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>T14.3.12</t>
+          <t>T14.3.13</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.12</t>
+          <t>Table 14.3.13</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by Age Group Subgroup</t>
+          <t>TEAEs by Sex Subgroup</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3955,7 +3959,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>t_ae_age.sas</t>
+          <t>t_ae_sex.sas</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3978,17 +3982,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>T14.3.13</t>
+          <t>T14.3.14</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.13</t>
+          <t>Table 14.3.14</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>TEAEs by Sex Subgroup</t>
+          <t>Hy's Law Cases — Liver Chemistry Screening</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4003,7 +4007,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>Safety Population with Baseline and Post-Baseline Labs</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4013,19 +4017,15 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>t_ae_sex.sas</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]</t>
-        </is>
-      </c>
+          <t>t_hys_law.sas</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4041,17 +4041,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>T14.3.14</t>
+          <t>T14.3.15</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.14</t>
+          <t>Table 14.3.15</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Hy's Law Cases — Liver Chemistry Screening</t>
+          <t>Laboratory Parameters — Shift Table (Baseline to Worst Post-Baseline)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with Baseline and Post-Baseline Labs</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4081,10 +4081,14 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>t_hys_law.sas</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr"/>
+          <t>t_lab_shift.sas</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4100,17 +4104,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>T14.3.15</t>
+          <t>T14.3.16</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.15</t>
+          <t>Table 14.3.16</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Parameters — Shift Table (Baseline to Worst Post-Baseline)</t>
+          <t>Hematology Parameters — Summary Statistics by Visit</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4140,14 +4144,10 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>t_lab_shift.sas</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>CTCAE [xx]</t>
-        </is>
-      </c>
+          <t>t_heme_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4163,17 +4163,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>T14.3.16</t>
+          <t>T14.3.17</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.16</t>
+          <t>Table 14.3.17</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Hematology Parameters — Summary Statistics by Visit</t>
+          <t>Clinical Chemistry Parameters — Summary Statistics by Visit</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>t_heme_by_visit.sas</t>
+          <t>t_chem_by_visit.sas</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -4222,17 +4222,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>T14.3.17</t>
+          <t>T14.3.18</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.17</t>
+          <t>Table 14.3.18</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Clinical Chemistry Parameters — Summary Statistics by Visit</t>
+          <t>Laboratory Abnormalities — Grade &gt;=3 Listing</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4262,10 +4262,14 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>t_chem_by_visit.sas</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr"/>
+          <t>l_lab_grade3.sas</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4281,17 +4285,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>T14.3.18</t>
+          <t>T14.3.19</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.18</t>
+          <t>Table 14.3.19</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Abnormalities — Grade &gt;=3 Listing</t>
+          <t>Laboratory Toxicity Grade Shift Over Time (by Cycle)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4321,7 +4325,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>l_lab_grade3.sas</t>
+          <t>t_lab_shift_cycle.sas</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4342,82 +4346,82 @@
       <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>T14.3.19</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.3.19</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Laboratory Toxicity Grade Shift Over Time (by Cycle)</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>F14.3.1</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.3.1</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Mean (+/- SD) Change in Laboratory Parameters Over Time</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADLB</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>t_lab_shift_cycle.sas</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>CTCAE [xx]</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>f_lab_longitudinal.sas</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>F14.3.1</t>
+          <t>F14.3.2</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.3.1</t>
+          <t>Figure 14.3.2</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Mean (+/- SD) Change in Laboratory Parameters Over Time</t>
+          <t>Box Plot — Liver Function Tests by Visit</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -4447,7 +4451,7 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>f_lab_longitudinal.sas</t>
+          <t>f_lft_box.sas</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr"/>
@@ -4468,82 +4472,78 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>F14.3.2</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.3.2</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Box Plot — Liver Function Tests by Visit</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.20</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.20</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Vital Signs — Summary Statistics by Visit</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADLB</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>f_lft_box.sas</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr"/>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>t_vs_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>T14.3.20</t>
+          <t>T14.3.21</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.20</t>
+          <t>Table 14.3.21</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Vital Signs — Summary Statistics by Visit</t>
+          <t>Vital Signs — Clinically Notable Abnormalities by Visit</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>t_vs_by_visit.sas</t>
+          <t>t_vs_notable.sas</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -4590,78 +4590,82 @@
       <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>T14.3.21</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.3.21</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Vital Signs — Clinically Notable Abnormalities by Visit</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>F14.3.3</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.3.3</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Mean (+/- SD) Vital Signs Over Time</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>Safety Population</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADVS</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>t_vs_notable.sas</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>f_vs_longitudinal.sas</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>F14.3.3</t>
+          <t>F14.3.4</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.3.3</t>
+          <t>Figure 14.3.4</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Mean (+/- SD) Vital Signs Over Time</t>
+          <t>Liver Function Panel — Mean Over Time with ULN Reference</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -4686,12 +4690,12 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADVS</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>f_vs_longitudinal.sas</t>
+          <t>f_lft_uln.sas</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
@@ -4712,82 +4716,78 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>F14.3.4</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.3.4</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Liver Function Panel — Mean Over Time with ULN Reference</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.22</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.22</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>ECG Parameters — Summary Statistics by Visit</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADLB</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>f_lft_uln.sas</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr"/>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ECG Data</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADEG</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>t_ecg_by_visit.sas</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>T14.3.22</t>
+          <t>T14.3.23</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.22</t>
+          <t>Table 14.3.23</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ECG Parameters — Summary Statistics by Visit</t>
+          <t>ECG QTcF Categorical Analysis</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>t_ecg_by_visit.sas</t>
+          <t>t_qtcf_cat.sas</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -4836,17 +4836,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>T14.3.23</t>
+          <t>T14.3.24</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.23</t>
+          <t>Table 14.3.24</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ECG QTcF Categorical Analysis</t>
+          <t>ECG Qualitative Assessment — Shift Table</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>t_qtcf_cat.sas</t>
+          <t>t_ecg_shift.sas</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -4895,17 +4895,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>T14.3.24</t>
+          <t>T14.3.25</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.24</t>
+          <t>Table 14.3.25</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ECG Qualitative Assessment — Shift Table</t>
+          <t>Infusion-Related Reactions by Preferred Term</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ECG Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4930,15 +4930,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADEG</t>
+          <t>ADSL, ADAE, ADEX</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>t_ecg_shift.sas</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr"/>
+          <t>t_irr.sas</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -4954,17 +4958,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>T14.3.25</t>
+          <t>T14.3.26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.25</t>
+          <t>Table 14.3.26</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Infusion-Related Reactions by Preferred Term</t>
+          <t>ECOG Performance Status Shift Table</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4989,19 +4993,15 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADEX</t>
+          <t>ADSL, ADQS</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>t_irr.sas</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
-        </is>
-      </c>
+          <t>t_ecog_shift.sas</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5017,17 +5017,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>T14.3.26</t>
+          <t>T14.3.27</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.26</t>
+          <t>Table 14.3.27</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>ECOG Performance Status Shift Table</t>
+          <t>Adverse Events of Special Interest (AESI) — Summary</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5052,15 +5052,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADQS</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>t_ecog_shift.sas</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr"/>
+          <t>t_aesi_summary.sas</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5076,17 +5080,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>T14.3.27</t>
+          <t>T14.3.28</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.27</t>
+          <t>Table 14.3.28</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Adverse Events of Special Interest (AESI) — Summary</t>
+          <t>AESI — Time to First Occurrence</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5116,7 +5120,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>t_aesi_summary.sas</t>
+          <t>t_aesi_ttf.sas</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5139,17 +5143,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>T14.3.28</t>
+          <t>T14.3.29</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.28</t>
+          <t>Table 14.3.29</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>AESI — Time to First Occurrence</t>
+          <t>Laboratory Parameters — Descriptive Statistics and Change from Baseline by Visit</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5174,17 +5178,17 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADAE</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>t_aesi_ttf.sas</t>
+          <t>t_lab_chg_bl.sas</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+          <t>CTCAE [xx]</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5202,17 +5206,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>T14.3.29</t>
+          <t>T14.3.30</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.29</t>
+          <t>Table 14.3.30</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Parameters — Descriptive Statistics and Change from Baseline by Visit</t>
+          <t>Laboratory Parameters — CTCAE Grade Shift (Baseline to Worst Post-Baseline)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5242,7 +5246,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>t_lab_chg_bl.sas</t>
+          <t>t_lab_grade_shift.sas</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5265,17 +5269,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>T14.3.30</t>
+          <t>T14.3.31</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Table 14.3.30</t>
+          <t>Table 14.3.31</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Laboratory Parameters — CTCAE Grade Shift (Baseline to Worst Post-Baseline)</t>
+          <t>TEAEs by Worst CTCAE Grade and System Organ Class</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5300,17 +5304,17 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADLB</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>t_lab_grade_shift.sas</t>
+          <t>t_ae_worst_grade.sas</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>CTCAE [xx]</t>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -5328,17 +5332,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>T14.4.1</t>
+          <t>T14.3.32</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.1</t>
+          <t>Table 14.3.32</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Summary of Pharmacokinetic Concentrations by Timepoint</t>
+          <t>TEAEs by Preferred Term — Full Frequency Listing (All PTs)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5348,12 +5352,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -5363,15 +5367,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPC</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>t_pk_conc.sas</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
+          <t>t_ae_pt_full.sas</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5387,17 +5395,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>T14.4.2</t>
+          <t>T14.3.33</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.2</t>
+          <t>Table 14.3.33</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Summary of Pharmacokinetic Parameters</t>
+          <t>TEAEs — Maximum Severity by Relationship to Study Drug</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5407,12 +5415,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -5422,15 +5430,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPP</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>t_pk_params.sas</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr"/>
+          <t>t_ae_sev_rel.sas</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5446,17 +5458,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>T14.4.3</t>
+          <t>T14.3.34</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.3</t>
+          <t>Table 14.3.34</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Summary of Anti-Drug Antibody (ADA) Incidence</t>
+          <t>Time to Onset of TEAEs by System Organ Class</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5466,12 +5478,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -5481,15 +5493,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>t_ada_incidence.sas</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr"/>
+          <t>t_ae_time_onset.sas</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5505,17 +5521,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>T14.4.4</t>
+          <t>T14.3.35</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.4</t>
+          <t>Table 14.3.35</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Summary of Biomarker Results by Visit</t>
+          <t>Duration of TEAEs by System Organ Class</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5525,12 +5541,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>ITT Population with Biomarker Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -5540,15 +5556,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>t_biomarker_visit.sas</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr"/>
+          <t>t_ae_duration.sas</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5564,17 +5584,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>T14.4.5</t>
+          <t>T14.3.36</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.5</t>
+          <t>Table 14.3.36</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Summary of Patient-Reported Outcomes by Visit</t>
+          <t>TEAEs by Preferred Term and Maximum CTCAE Grade — Group 2</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5584,12 +5604,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>ITT Population with PRO Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -5599,15 +5619,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPRO</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>t_pro_summary.sas</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
+          <t>t_ae_grade_g2.sas</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5623,17 +5647,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>T14.4.6</t>
+          <t>T14.3.37</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.6</t>
+          <t>Table 14.3.37</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Summary of Pharmacodynamics — Soluble Biomarkers by Visit</t>
+          <t>TEAEs by Cycle — Detailed On-Treatment Period Analysis</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5643,12 +5667,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>PD Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -5658,15 +5682,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADPD</t>
+          <t>ADSL, ADAE, ADEX</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>t_pd_summary.sas</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr"/>
+          <t>t_ae_by_cycle_detail.sas</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -5682,1170 +5710,1166 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>T14.3.38</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.38</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Parameters — Clinically Significant Abnormalities Summary</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>t_lab_cs_abn.sas</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.39</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.39</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Hematology — Shift Table by CTCAE Grade (Baseline to Worst Post-Baseline) — Detailed</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>t_heme_shift_detail.sas</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.40</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.40</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Chemistry — Shift Table (Normal Range Based) — Baseline to Worst Post-Baseline</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>t_chem_shift_nr.sas</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.41</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.41</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Vital Signs — Shift Table (Normal to Clinically Notable)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS, ADEG</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>t_vs_shift.sas</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.42</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.42</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Body Weight — Change from Baseline by Visit</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>t_weight_chg.sas</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.43</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.43</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>ECG Parameters — Quantitative Change from Baseline by Visit</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ECG Data</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADEG</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>t_ecg_chg_bl.sas</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.44</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.44</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Parameters — Worst Post-Baseline Value by Visit Group</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>t_lab_worst_visit.sas</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.45</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.45</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Adverse Events — Summary of Multiple Occurrences per Subject</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_mult_occ.sas</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.1</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Pharmacokinetic Concentrations by Timepoint</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>t_pk_conc.sas</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.2</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Pharmacokinetic Parameters</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPP</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>t_pk_params.sas</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.3</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.3</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Anti-Drug Antibody (ADA) Incidence</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>t_ada_incidence.sas</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.4</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.4</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Biomarker Results by Visit</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population with Biomarker Data</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADBM</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>t_biomarker_visit.sas</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.5</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.5</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Patient-Reported Outcomes by Visit</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>ITT Population with PRO Data</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>t_pro_summary.sas</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.6</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.6</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Summary of Pharmacodynamics — Soluble Biomarkers by Visit</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>PD Population</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPD</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>t_pd_summary.sas</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
           <t>T14.4.7</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Table 14.4.7</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Summary of Central Molecular Test Results and Gene Aberrations at Baseline</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Full Analysis Set</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>ADSL, ADBM</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>t_gene_aberrations.sas</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>F14.4.1</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.1</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>PK Population</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADPC</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>f_pk_profile.sas</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr"/>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="inlineStr">
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>F14.4.2</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.2</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Overlaying Individual PK Concentration Profiles</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>PK Population</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADPC</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>f_pk_overlay.sas</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr"/>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>F14.4.3</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.3</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>PD Population</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADPD</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>f_pd_time.sas</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr"/>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>F14.4.4</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.4</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Boxplot of Biomarkers at Baseline vs. Response Status</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>Full Analysis Set with Biomarker Data</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADBM</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t>f_biomarker_box.sas</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr"/>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L90" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M90" s="3" t="inlineStr">
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.1</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.1</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Subject Disposition</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>All Screened Subjects</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>l_disposition.sas</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr"/>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M91" s="4" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.2</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.2</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Demographic Data</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>All Randomized Subjects</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>l_demog.sas</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.3</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.3</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Protocol Deviations</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>All Enrolled Subjects</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, DV</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>l_protdev.sas</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr"/>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.4</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.4</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Adverse Events</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADAE</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>l_ae.sas</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
-        </is>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M94" s="4" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.5</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.5</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Serious Adverse Events</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADAE</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>l_sae.sas</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]; CTCAE [xx]</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M95" s="4" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.6</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.6</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Concomitant Medications</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADCM</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>l_conmed.sas</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>WHO-DD [version]</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M96" s="4" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.7</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.7</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Laboratory Data — Hematology and Chemistry</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADLB</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>l_lab.sas</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr"/>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M97" s="4" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.8</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.8</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Vital Signs</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADVS</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>l_vitalsigns.sas</t>
-        </is>
-      </c>
-      <c r="J98" s="4" t="inlineStr"/>
-      <c r="K98" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M98" s="4" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.9</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.9</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>Listing of ECG Data</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population with ECG Data</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADEG</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>l_ecg.sas</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr"/>
-      <c r="K99" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M99" s="4" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.10</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.10</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Tumor Response Data</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>ITT Population</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADRS</t>
-        </is>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t>l_tumor_response.sas</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M100" s="4" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.11</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.11</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Survival Data</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>ITT Population</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADTTE</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>l_survival.sas</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr"/>
-      <c r="K101" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M101" s="4" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.12</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.12</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Study Drug Exposure and Dose Modifications</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADEX</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>l_exposure.sas</t>
-        </is>
-      </c>
-      <c r="J102" s="4" t="inlineStr"/>
-      <c r="K102" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M102" s="4" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.13</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.13</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>Listing of Medical History Verbatim vs. Coded Terms</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADMH</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t>l_mh_coded.sas</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>MedDRA [xx.x]</t>
-        </is>
-      </c>
-      <c r="K103" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M103" s="4" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>L16.2.14</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>Listing 16.2.14</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Listing of PK Concentrations by Subject and Timepoint</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>Listing</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>l_pk_conc.sas</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>L16.2.15</t>
+          <t>L16.2.1</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.15</t>
+          <t>Listing 16.2.1</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Listing of PK Parameters by Subject</t>
+          <t>Listing of Subject Disposition</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -6860,7 +6884,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>PK Population</t>
+          <t>All Screened Subjects</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -6870,12 +6894,12 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPP</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>l_pk_params.sas</t>
+          <t>l_disposition.sas</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr"/>
@@ -6894,17 +6918,17 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>L16.2.16</t>
+          <t>L16.2.2</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.16</t>
+          <t>Listing 16.2.2</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Listing of ADA and Neutralizing Antibody Results</t>
+          <t>Listing of Demographic Data</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6919,7 +6943,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>All Randomized Subjects</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6929,12 +6953,12 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>l_ada.sas</t>
+          <t>l_demog.sas</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr"/>
@@ -6953,17 +6977,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>L16.2.17</t>
+          <t>L16.2.3</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.17</t>
+          <t>Listing 16.2.3</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Listing of Biomarker Results by Subject and Visit</t>
+          <t>Listing of Protocol Deviations</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6978,7 +7002,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>ITT with Biomarker Data</t>
+          <t>All Enrolled Subjects</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -6988,12 +7012,12 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADBM</t>
+          <t>ADSL, DV</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>l_biomarker.sas</t>
+          <t>l_protdev.sas</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr"/>
@@ -7012,17 +7036,17 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>L16.2.18</t>
+          <t>L16.2.4</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.18</t>
+          <t>Listing 16.2.4</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Listing of PRO Assessments by Subject and Visit</t>
+          <t>Listing of Adverse Events</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -7037,7 +7061,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>ITT with PRO Data</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -7047,15 +7071,19 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADPRO</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>l_pro.sas</t>
-        </is>
-      </c>
-      <c r="J108" s="4" t="inlineStr"/>
+          <t>l_ae.sas</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -7071,17 +7099,17 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>L16.2.19</t>
+          <t>L16.2.5</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.19</t>
+          <t>Listing 16.2.5</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+          <t>Listing of Serious Adverse Events</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -7096,25 +7124,29 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>ITT Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL, ADAE</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>l_subsequent_therapy.sas</t>
-        </is>
-      </c>
-      <c r="J109" s="4" t="inlineStr"/>
+          <t>l_sae.sas</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -7130,17 +7162,17 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>L16.2.20</t>
+          <t>L16.2.6</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.20</t>
+          <t>Listing 16.2.6</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Listing of Deaths — All Subjects</t>
+          <t>Listing of Concomitant Medications</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -7155,7 +7187,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>All Randomized Subjects</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -7165,15 +7197,19 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADAE, ADTTE</t>
+          <t>ADSL, ADCM</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>l_deaths.sas</t>
-        </is>
-      </c>
-      <c r="J110" s="4" t="inlineStr"/>
+          <t>l_conmed.sas</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>WHO-DD [version]</t>
+        </is>
+      </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
           <t>First column retained; non-structural cells use XX</t>
@@ -7189,17 +7225,17 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>L16.2.21</t>
+          <t>L16.2.7</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Listing 16.2.21</t>
+          <t>Listing 16.2.7</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Listing of Prior and Subsequent Anti-Cancer Surgery/Radiotherapy</t>
+          <t>Listing of Laboratory Data — Hematology and Chemistry</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -7214,22 +7250,22 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Full Analysis Set</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>ADSL, ADCM</t>
+          <t>ADSL, ADLB</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>l_prior_cancer_proc.sas</t>
+          <t>l_lab.sas</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr"/>
@@ -7245,8 +7281,838 @@
       </c>
       <c r="M111" s="4" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.8</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.8</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Vital Signs</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>l_vitalsigns.sas</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.9</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.9</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Listing of ECG Data</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Safety Population with ECG Data</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADEG</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>l_ecg.sas</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr"/>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.10</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.10</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Tumor Response Data</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>l_tumor_response.sas</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.11</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.11</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Survival Data</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>l_survival.sas</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.12</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.12</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Study Drug Exposure and Dose Modifications</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADEX</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>l_exposure.sas</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr"/>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.13</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.13</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Medical History Verbatim vs. Coded Terms</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADMH</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>l_mh_coded.sas</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.14</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.14</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Listing of PK Concentrations by Subject and Timepoint</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>l_pk_conc.sas</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.15</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.15</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Listing of PK Parameters by Subject</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADPP</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>l_pk_params.sas</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.16</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.16</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Listing of ADA and Neutralizing Antibody Results</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>l_ada.sas</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.17</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.17</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Biomarker Results by Subject and Visit</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>ITT with Biomarker Data</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADBM</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>l_biomarker.sas</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.18</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.18</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Listing of PRO Assessments by Subject and Visit</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>ITT with PRO Data</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADPRO</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>l_pro.sas</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.19</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.19</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Subsequent Anti-Cancer Therapies</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>ITT Population</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>l_subsequent_therapy.sas</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.20</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.20</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Deaths — All Subjects</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>All Randomized Subjects</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE, ADTTE</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>l_deaths.sas</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>L16.2.21</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Listing 16.2.21</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Listing of Prior and Subsequent Anti-Cancer Surgery/Radiotherapy</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Full Analysis Set</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>ADSL, ADCM</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>l_prior_cancer_proc.sas</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M125" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M111"/>
+  <autoFilter ref="A1:M125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -7258,7 +8124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7903,7 +8769,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COVID-19 Medical History, Vaccination, and Testing Status</t>
+          <t>Summary of Study Drug Exposure — Duration, Cycles, Dose Intensity</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -7928,12 +8794,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADMH</t>
+          <t>ADEX</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>t_covid19_status.sas</t>
+          <t>t_exposure_summary.sas</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -7962,7 +8828,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Summary of Study Drug Exposure — Duration, Cycles, Dose Intensity</t>
+          <t>Summary of Genomic/Biomarker Baseline Characteristics</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -7977,22 +8843,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT Population with Biomarker Data</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>ADEX</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>t_exposure_summary.sas</t>
+          <t>t_biomarker_baseline.sas</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -8008,67 +8874,8 @@
       </c>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>T14.1.12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.1.12</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Summary of Genomic/Biomarker Baseline Characteristics</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>ITT Population with Biomarker Data</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADBM</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>t_biomarker_baseline.sas</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -10106,7 +10913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12293,8 +13100,933 @@
       </c>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.31</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.31</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>TEAEs by Worst CTCAE Grade and System Organ Class</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_worst_grade.sas</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.32</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.32</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>TEAEs by Preferred Term — Full Frequency Listing (All PTs)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_pt_full.sas</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.33</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.33</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>TEAEs — Maximum Severity by Relationship to Study Drug</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_sev_rel.sas</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.34</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.34</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Time to Onset of TEAEs by System Organ Class</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_time_onset.sas</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.35</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.35</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Duration of TEAEs by System Organ Class</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_duration.sas</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.36</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.36</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>TEAEs by Preferred Term and Maximum CTCAE Grade — Group 2</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_grade_g2.sas</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.37</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.37</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>TEAEs by Cycle — Detailed On-Treatment Period Analysis</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE, ADEX</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_by_cycle_detail.sas</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.38</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.38</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Parameters — Clinically Significant Abnormalities Summary</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>t_lab_cs_abn.sas</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.39</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.39</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Hematology — Shift Table by CTCAE Grade (Baseline to Worst Post-Baseline) — Detailed</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>t_heme_shift_detail.sas</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.40</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.40</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Chemistry — Shift Table (Normal Range Based) — Baseline to Worst Post-Baseline</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>t_chem_shift_nr.sas</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.41</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.41</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Vital Signs — Shift Table (Normal to Clinically Notable)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS, ADEG</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>t_vs_shift.sas</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.42</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.42</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Body Weight — Change from Baseline by Visit</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADVS</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>t_weight_chg.sas</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.43</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.43</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>ECG Parameters — Quantitative Change from Baseline by Visit</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ECG Data</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADEG</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>t_ecg_chg_bl.sas</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.44</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.44</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Parameters — Worst Post-Baseline Value by Visit Group</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADLB</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>t_lab_worst_visit.sas</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>T14.3.45</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.3.45</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Adverse Events — Summary of Multiple Occurrences per Subject</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADAE</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>t_ae_mult_occ.sas</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>MedDRA [xx.x]; CTCAE [xx]</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M35"/>
+  <autoFilter ref="A1:M50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/output/TFL_TOC_v2.1.0.xlsx
+++ b/output/TFL_TOC_v2.1.0.xlsx
@@ -2067,208 +2067,196 @@
       <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.1</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.1</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Forest Plot — Primary Endpoint by Subgroup</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.9</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.9</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Tumor Response — Best Overall Response (BOR)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADEFF</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>f_forest_primary.sas</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>t_bor.sas</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.2</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.2</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Longitudinal Plot — Primary Endpoint Over Time</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.10</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.10</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Tumor Response — Objective Response Rate (ORR)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADEFF</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>f_longitudinal_eff.sas</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>t_orr.sas</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.3</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.3</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.11</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.11</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Tumor Response — Disease Control Rate (DCR)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADEFF</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>f_cdf_eff.sas</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>t_dcr.sas</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>T14.2.9</t>
+          <t>T14.2.12</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.9</t>
+          <t>Table 14.2.12</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Best Overall Response (BOR)</t>
+          <t>Tumor Response — Duration of Response (DOR)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2283,7 +2271,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Responders (Confirmed CR or PR)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2293,12 +2281,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADRS, ADTTE</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>t_bor.sas</t>
+          <t>t_dor.sas</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2317,17 +2305,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>T14.2.10</t>
+          <t>T14.2.13</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.10</t>
+          <t>Table 14.2.13</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Objective Response Rate (ORR)</t>
+          <t>Tumor Response — Time to Response (TTR)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2342,7 +2330,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Responders (Confirmed CR or PR)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2357,7 +2345,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>t_orr.sas</t>
+          <t>t_ttr.sas</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2376,17 +2364,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>T14.2.11</t>
+          <t>T14.2.14</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.11</t>
+          <t>Table 14.2.14</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Disease Control Rate (DCR)</t>
+          <t>Progression-Free Survival (PFS) — Primary Analysis</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2411,12 +2399,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>t_dcr.sas</t>
+          <t>t_pfs_primary.sas</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2435,17 +2423,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>T14.2.12</t>
+          <t>T14.2.15</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.12</t>
+          <t>Table 14.2.15</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Duration of Response (DOR)</t>
+          <t>Overall Survival (OS) — Primary Analysis</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2460,7 +2448,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Responders (Confirmed CR or PR)</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2470,12 +2458,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS, ADTTE</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>t_dor.sas</t>
+          <t>t_os_primary.sas</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -2494,17 +2482,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>T14.2.13</t>
+          <t>T14.2.16</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.13</t>
+          <t>Table 14.2.16</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Time to Response (TTR)</t>
+          <t>PFS — Sensitivity Analysis</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2519,7 +2507,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Responders (Confirmed CR or PR)</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2529,12 +2517,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>t_ttr.sas</t>
+          <t>t_pfs_sensitivity.sas</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2553,17 +2541,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>T14.2.14</t>
+          <t>T14.2.17</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.14</t>
+          <t>Table 14.2.17</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Progression-Free Survival (PFS) — Primary Analysis</t>
+          <t>PFS — Subgroup Analysis</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2593,7 +2581,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_primary.sas</t>
+          <t>t_pfs_subgroup.sas</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -2612,17 +2600,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>T14.2.15</t>
+          <t>T14.2.18</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.15</t>
+          <t>Table 14.2.18</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Overall Survival (OS) — Primary Analysis</t>
+          <t>OS — Subgroup Analysis</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2652,7 +2640,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>t_os_primary.sas</t>
+          <t>t_os_subgroup.sas</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2671,17 +2659,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>T14.2.16</t>
+          <t>T14.2.19</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.16</t>
+          <t>Table 14.2.19</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PFS — Sensitivity Analysis</t>
+          <t>Summary of Target Lesion Changes from Baseline</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2696,7 +2684,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2706,12 +2694,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_sensitivity.sas</t>
+          <t>t_target_lesion.sas</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -2730,17 +2718,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>T14.2.17</t>
+          <t>T14.2.20</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.17</t>
+          <t>Table 14.2.20</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>PFS — Subgroup Analysis</t>
+          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2755,7 +2743,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT Alive and On-Study at 6 Months</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2770,7 +2758,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_subgroup.sas</t>
+          <t>t_landmark_os.sas</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2789,17 +2777,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>T14.2.18</t>
+          <t>T14.2.21</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.18</t>
+          <t>Table 14.2.21</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>OS — Subgroup Analysis</t>
+          <t>Time to First Subsequent Therapy (TFST)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2814,7 +2802,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2824,12 +2812,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADTTE, ADCM</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>t_os_subgroup.sas</t>
+          <t>t_tfst.sas</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -2848,17 +2836,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>T14.2.19</t>
+          <t>T14.2.22</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.19</t>
+          <t>Table 14.2.22</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Summary of Target Lesion Changes from Baseline</t>
+          <t>PK/PD Exposure-Response Correlation Analysis</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2873,22 +2861,22 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
+          <t>PK/PD Evaluable Population</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADPK, ADEFF</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>t_target_lesion.sas</t>
+          <t>t_pkpd_corr.sas</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2905,137 +2893,145 @@
       <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.20</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.20</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.1</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.1</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — Primary Endpoint by Subgroup</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>ITT Alive and On-Study at 6 Months</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADTTE</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>t_landmark_os.sas</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADEFF</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_primary.sas</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.21</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.21</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Time to First Subsequent Therapy (TFST)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.2</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.2</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Longitudinal Plot — Primary Endpoint Over Time</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>ITT Population</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADTTE, ADCM</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>t_tfst.sas</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADEFF</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>f_longitudinal_eff.sas</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>F14.2.4</t>
+          <t>F14.2.3</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.4</t>
+          <t>Figure 14.2.3</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
+          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3050,22 +3046,22 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADEFF</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>f_waterfall.sas</t>
+          <t>f_cdf_eff.sas</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
@@ -3088,17 +3084,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>F14.2.5</t>
+          <t>F14.2.4</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.5</t>
+          <t>Figure 14.2.4</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
+          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3113,7 +3109,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease</t>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3128,7 +3124,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>f_spider.sas</t>
+          <t>f_waterfall.sas</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr"/>
@@ -3151,17 +3147,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>F14.2.6</t>
+          <t>F14.2.5</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.6</t>
+          <t>Figure 14.2.5</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Swimmer Plot — Duration of Treatment and Response</t>
+          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3176,7 +3172,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT with Measurable Disease</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3186,12 +3182,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADEX, ADRS</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>f_swimmer.sas</t>
+          <t>f_spider.sas</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr"/>
@@ -3214,17 +3210,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>F14.2.7</t>
+          <t>F14.2.6</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.7</t>
+          <t>Figure 14.2.6</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
+          <t>Swimmer Plot — Duration of Treatment and Response</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3239,7 +3235,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3249,12 +3245,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADEX, ADRS</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>f_km_pfs.sas</t>
+          <t>f_swimmer.sas</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr"/>
@@ -3277,17 +3273,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>F14.2.8</t>
+          <t>F14.2.7</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.8</t>
+          <t>Figure 14.2.7</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Overall Survival</t>
+          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3317,7 +3313,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>f_km_os.sas</t>
+          <t>f_km_pfs.sas</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
@@ -3340,17 +3336,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>F14.2.9</t>
+          <t>F14.2.8</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.9</t>
+          <t>Figure 14.2.8</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — PFS by Subgroup</t>
+          <t>Kaplan-Meier Plot — Overall Survival</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>f_forest_pfs.sas</t>
+          <t>f_km_os.sas</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr"/>
@@ -3403,17 +3399,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>F14.2.10</t>
+          <t>F14.2.9</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.10</t>
+          <t>Figure 14.2.9</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — OS by Subgroup</t>
+          <t>Forest Plot — PFS by Subgroup</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -3443,7 +3439,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>f_forest_os.sas</t>
+          <t>f_forest_pfs.sas</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr"/>
@@ -3464,63 +3460,67 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.22</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.22</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Exposure-Response Correlation Analysis</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.10</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.10</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — OS by Subgroup</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Evaluable Population</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPK, ADEFF</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>t_pkpd_corr.sas</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_os.sas</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9135,82 +9135,78 @@
       <c r="M142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>F14.4.1</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.4.1</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.8</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.8</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>ADA Titer Distribution by Visit — Negative, Low, Medium, High</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>f_pk_profile.sas</t>
-        </is>
-      </c>
-      <c r="J143" s="3" t="inlineStr"/>
-      <c r="K143" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L143" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M143" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>t_ada_titer.sas</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>T14.4.8</t>
+          <t>T14.4.9</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.8</t>
+          <t>Table 14.4.9</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>ADA Titer Distribution by Visit — Negative, Low, Medium, High</t>
+          <t>ADA Impact on Pharmacokinetics — Cmax and AUC in ADA+ vs. ADA- Subjects</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -9225,7 +9221,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>PK Population with ADA Data</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -9235,12 +9231,12 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADIS, ADPP</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>t_ada_titer.sas</t>
+          <t>t_ada_pk_impact.sas</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
@@ -9257,82 +9253,78 @@
       <c r="M144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>F14.4.2</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.4.2</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>Overlaying Individual PK Concentration Profiles</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.10</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.10</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Neutralizing Antibody (Nab) — Incidence, Titer, and Cross-Reactivity Status</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>f_pk_overlay.sas</t>
-        </is>
-      </c>
-      <c r="J145" s="3" t="inlineStr"/>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M145" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>t_nab_detail.sas</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>T14.4.9</t>
+          <t>T14.4.11</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.9</t>
+          <t>Table 14.4.11</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>ADA Impact on Pharmacokinetics — Cmax and AUC in ADA+ vs. ADA- Subjects</t>
+          <t>Soluble Pharmacodynamic Biomarker Change from Baseline Over Time</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -9347,7 +9339,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>PK Population with ADA Data</t>
+          <t>PD Population</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -9357,12 +9349,12 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS, ADPP</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>t_ada_pk_impact.sas</t>
+          <t>t_pd_bio_chg.sas</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
@@ -9379,82 +9371,78 @@
       <c r="M146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>F14.4.3</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.4.3</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.12</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.12</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Trough PK Concentration (Ctrough) by Cycle — Target Attainment</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>PD Population</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADPD</t>
-        </is>
-      </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>f_pd_time.sas</t>
-        </is>
-      </c>
-      <c r="J147" s="3" t="inlineStr"/>
-      <c r="K147" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M147" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>t_ctrough.sas</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>T14.4.10</t>
+          <t>T14.4.13</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.10</t>
+          <t>Table 14.4.13</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Neutralizing Antibody (Nab) — Incidence, Titer, and Cross-Reactivity Status</t>
+          <t>Steady-State Attainment — Trough Concentrations Across Dosing Cycles (ANOVA)</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -9469,7 +9457,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -9479,12 +9467,12 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADPC</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>t_nab_detail.sas</t>
+          <t>t_steady_state.sas</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
@@ -9501,303 +9489,315 @@
       <c r="M148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.14</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.14</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Urine Pharmacokinetic Parameters — Renal Excretion and Cumulative Recovery</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>PK Population (Subset with Urine PK)</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPP</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>t_urine_pk.sas</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.1</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.1</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_profile.sas</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.2</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.2</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Overlaying Individual PK Concentration Profiles</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_overlay.sas</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.3</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.3</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>PD Population</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPD</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>f_pd_time.sas</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr"/>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>F14.4.4</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.4</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t>Boxplot of Biomarkers at Baseline vs. Response Status</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>Full Analysis Set with Biomarker Data</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr">
+      <c r="G153" s="3" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H153" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADBM</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
+      <c r="I153" s="3" t="inlineStr">
         <is>
           <t>f_biomarker_box.sas</t>
         </is>
       </c>
-      <c r="J149" s="3" t="inlineStr"/>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M149" s="3" t="inlineStr">
+      <c r="J153" s="3" t="inlineStr"/>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.11</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.11</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Soluble Pharmacodynamic Biomarker Change from Baseline Over Time</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>PD Population</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADBM</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>t_pd_bio_chg.sas</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr"/>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.12</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.12</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Trough PK Concentration (Ctrough) by Cycle — Target Attainment</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>t_ctrough.sas</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.13</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.13</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Steady-State Attainment — Trough Concentrations Across Dosing Cycles (ANOVA)</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>t_steady_state.sas</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr"/>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.14</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.14</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Urine Pharmacokinetic Parameters — Renal Excretion and Cumulative Recovery</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>PK Population (Subset with Urine PK)</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPP</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>t_urine_pk.sas</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr"/>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -13344,208 +13344,196 @@
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.1</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.1</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Forest Plot — Primary Endpoint by Subgroup</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Tumor Response — Best Overall Response (BOR)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADEFF</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>f_forest_primary.sas</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>t_bor.sas</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.2</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.2</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Longitudinal Plot — Primary Endpoint Over Time</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tumor Response — Objective Response Rate (ORR)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADEFF</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>f_longitudinal_eff.sas</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>t_orr.sas</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>F14.2.3</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.2.3</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>T14.2.11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.2.11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Tumor Response — Disease Control Rate (DCR)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADEFF</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>f_cdf_eff.sas</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADRS</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>t_dcr.sas</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>T14.2.9</t>
+          <t>T14.2.12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.9</t>
+          <t>Table 14.2.12</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Best Overall Response (BOR)</t>
+          <t>Tumor Response — Duration of Response (DOR)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -13560,7 +13548,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Responders (Confirmed CR or PR)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13570,12 +13558,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADRS, ADTTE</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>t_bor.sas</t>
+          <t>t_dor.sas</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -13594,17 +13582,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T14.2.10</t>
+          <t>T14.2.13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.10</t>
+          <t>Table 14.2.13</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Objective Response Rate (ORR)</t>
+          <t>Tumor Response — Time to Response (TTR)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -13619,7 +13607,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Responders (Confirmed CR or PR)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13634,7 +13622,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>t_orr.sas</t>
+          <t>t_ttr.sas</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -13653,17 +13641,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T14.2.11</t>
+          <t>T14.2.14</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.11</t>
+          <t>Table 14.2.14</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Disease Control Rate (DCR)</t>
+          <t>Progression-Free Survival (PFS) — Primary Analysis</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -13688,12 +13676,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>t_dcr.sas</t>
+          <t>t_pfs_primary.sas</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -13712,17 +13700,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T14.2.12</t>
+          <t>T14.2.15</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.12</t>
+          <t>Table 14.2.15</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Duration of Response (DOR)</t>
+          <t>Overall Survival (OS) — Primary Analysis</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -13737,7 +13725,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Responders (Confirmed CR or PR)</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13747,12 +13735,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS, ADTTE</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>t_dor.sas</t>
+          <t>t_os_primary.sas</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -13771,17 +13759,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T14.2.13</t>
+          <t>T14.2.16</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.13</t>
+          <t>Table 14.2.16</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Tumor Response — Time to Response (TTR)</t>
+          <t>PFS — Sensitivity Analysis</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -13796,7 +13784,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Responders (Confirmed CR or PR)</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13806,12 +13794,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADTTE</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>t_ttr.sas</t>
+          <t>t_pfs_sensitivity.sas</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -13830,17 +13818,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T14.2.14</t>
+          <t>T14.2.17</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.14</t>
+          <t>Table 14.2.17</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Progression-Free Survival (PFS) — Primary Analysis</t>
+          <t>PFS — Subgroup Analysis</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -13870,7 +13858,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_primary.sas</t>
+          <t>t_pfs_subgroup.sas</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -13889,17 +13877,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>T14.2.15</t>
+          <t>T14.2.18</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.15</t>
+          <t>Table 14.2.18</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Overall Survival (OS) — Primary Analysis</t>
+          <t>OS — Subgroup Analysis</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -13929,7 +13917,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>t_os_primary.sas</t>
+          <t>t_os_subgroup.sas</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -13948,17 +13936,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>T14.2.16</t>
+          <t>T14.2.19</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.16</t>
+          <t>Table 14.2.19</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PFS — Sensitivity Analysis</t>
+          <t>Summary of Target Lesion Changes from Baseline</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -13973,7 +13961,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13983,12 +13971,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_sensitivity.sas</t>
+          <t>t_target_lesion.sas</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -14007,17 +13995,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>T14.2.17</t>
+          <t>T14.2.20</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.17</t>
+          <t>Table 14.2.20</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PFS — Subgroup Analysis</t>
+          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -14032,7 +14020,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT Alive and On-Study at 6 Months</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14047,7 +14035,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>t_pfs_subgroup.sas</t>
+          <t>t_landmark_os.sas</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -14066,17 +14054,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>T14.2.18</t>
+          <t>T14.2.21</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.18</t>
+          <t>Table 14.2.21</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>OS — Subgroup Analysis</t>
+          <t>Time to First Subsequent Therapy (TFST)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -14091,7 +14079,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>ITT Population</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14101,12 +14089,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADTTE, ADCM</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>t_os_subgroup.sas</t>
+          <t>t_tfst.sas</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -14125,17 +14113,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>T14.2.19</t>
+          <t>T14.2.22</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Table 14.2.19</t>
+          <t>Table 14.2.22</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Summary of Target Lesion Changes from Baseline</t>
+          <t>PK/PD Exposure-Response Correlation Analysis</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -14150,22 +14138,22 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
+          <t>PK/PD Evaluable Population</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADPK, ADEFF</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>t_target_lesion.sas</t>
+          <t>t_pkpd_corr.sas</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -14182,137 +14170,145 @@
       <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.20</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.20</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Landmark Analysis of OS by 6-Month PFS Status</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.1</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.1</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — Primary Endpoint by Subgroup</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>ITT Alive and On-Study at 6 Months</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADTTE</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>t_landmark_os.sas</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADEFF</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_primary.sas</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.21</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.21</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Time to First Subsequent Therapy (TFST)</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.2</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.2</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Longitudinal Plot — Primary Endpoint Over Time</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>ITT Population</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Oncology only</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADTTE, ADCM</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>t_tfst.sas</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADEFF</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>f_longitudinal_eff.sas</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F14.2.4</t>
+          <t>F14.2.3</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.4</t>
+          <t>Figure 14.2.3</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
+          <t>Cumulative Distribution Function Plot of Primary Endpoint</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -14327,22 +14323,22 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
+          <t>Intent-to-Treat (ITT) Population</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Oncology only</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADRS</t>
+          <t>ADSL, ADEFF</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>f_waterfall.sas</t>
+          <t>f_cdf_eff.sas</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -14365,17 +14361,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>F14.2.5</t>
+          <t>F14.2.4</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.5</t>
+          <t>Figure 14.2.4</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
+          <t>Waterfall Plot — Best Percentage Change in Target Lesions</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -14390,7 +14386,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>ITT with Measurable Disease</t>
+          <t>ITT with Measurable Disease and Post-Baseline Assessment</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -14405,7 +14401,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>f_spider.sas</t>
+          <t>f_waterfall.sas</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
@@ -14428,17 +14424,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F14.2.6</t>
+          <t>F14.2.5</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.6</t>
+          <t>Figure 14.2.5</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Swimmer Plot — Duration of Treatment and Response</t>
+          <t>Spider Plot — Percentage Change in Tumor Burden Over Time</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -14453,7 +14449,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Safety Population</t>
+          <t>ITT with Measurable Disease</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -14463,12 +14459,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADEX, ADRS</t>
+          <t>ADSL, ADRS</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>f_swimmer.sas</t>
+          <t>f_spider.sas</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -14491,17 +14487,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>F14.2.7</t>
+          <t>F14.2.6</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.7</t>
+          <t>Figure 14.2.6</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
+          <t>Swimmer Plot — Duration of Treatment and Response</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -14516,7 +14512,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Intent-to-Treat (ITT) Population</t>
+          <t>Safety Population</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -14526,12 +14522,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>ADSL, ADTTE</t>
+          <t>ADSL, ADEX, ADRS</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>f_km_pfs.sas</t>
+          <t>f_swimmer.sas</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -14554,17 +14550,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>F14.2.8</t>
+          <t>F14.2.7</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.8</t>
+          <t>Figure 14.2.7</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Kaplan-Meier Plot — Overall Survival</t>
+          <t>Kaplan-Meier Plot — Progression-Free Survival</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -14594,7 +14590,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>f_km_os.sas</t>
+          <t>f_km_pfs.sas</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
@@ -14617,17 +14613,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>F14.2.9</t>
+          <t>F14.2.8</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.9</t>
+          <t>Figure 14.2.8</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — PFS by Subgroup</t>
+          <t>Kaplan-Meier Plot — Overall Survival</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -14657,7 +14653,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>f_forest_pfs.sas</t>
+          <t>f_km_os.sas</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -14680,17 +14676,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>F14.2.10</t>
+          <t>F14.2.9</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Figure 14.2.10</t>
+          <t>Figure 14.2.9</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Forest Plot — OS by Subgroup</t>
+          <t>Forest Plot — PFS by Subgroup</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -14720,7 +14716,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>f_forest_os.sas</t>
+          <t>f_forest_pfs.sas</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
@@ -14741,63 +14737,67 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>T14.2.22</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.2.22</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Exposure-Response Correlation Analysis</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>F14.2.10</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.2.10</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Forest Plot — OS by Subgroup</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>PK/PD Evaluable Population</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPK, ADEFF</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>t_pkpd_corr.sas</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Intent-to-Treat (ITT) Population</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Oncology only</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADTTE</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>f_forest_os.sas</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M33"/>
@@ -20608,82 +20608,78 @@
       <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>F14.4.1</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.4.1</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ADA Titer Distribution by Visit — Negative, Low, Medium, High</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>f_pk_profile.sas</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>t_ada_titer.sas</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>T14.4.8</t>
+          <t>T14.4.9</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.8</t>
+          <t>Table 14.4.9</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ADA Titer Distribution by Visit — Negative, Low, Medium, High</t>
+          <t>ADA Impact on Pharmacokinetics — Cmax and AUC in ADA+ vs. ADA- Subjects</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -20698,7 +20694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>PK Population with ADA Data</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -20708,12 +20704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADIS, ADPP</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>t_ada_titer.sas</t>
+          <t>t_ada_pk_impact.sas</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -20730,82 +20726,78 @@
       <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>F14.4.2</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.4.2</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Overlaying Individual PK Concentration Profiles</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Neutralizing Antibody (Nab) — Incidence, Titer, and Cross-Reactivity Status</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>f_pk_overlay.sas</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Safety Population with ADA Samples</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADIS</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>t_nab_detail.sas</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>T14.4.9</t>
+          <t>T14.4.11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.9</t>
+          <t>Table 14.4.11</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ADA Impact on Pharmacokinetics — Cmax and AUC in ADA+ vs. ADA- Subjects</t>
+          <t>Soluble Pharmacodynamic Biomarker Change from Baseline Over Time</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -20820,7 +20812,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>PK Population with ADA Data</t>
+          <t>PD Population</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -20830,12 +20822,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS, ADPP</t>
+          <t>ADSL, ADBM</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>t_ada_pk_impact.sas</t>
+          <t>t_pd_bio_chg.sas</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -20852,82 +20844,78 @@
       <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>F14.4.3</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Figure 14.4.3</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Trough PK Concentration (Ctrough) by Cycle — Target Attainment</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>PD Population</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>ADSL, ADPD</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>f_pd_time.sas</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Simulated figure generated</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>t_ctrough.sas</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T14.4.10</t>
+          <t>T14.4.13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Table 14.4.10</t>
+          <t>Table 14.4.13</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Neutralizing Antibody (Nab) — Incidence, Titer, and Cross-Reactivity Status</t>
+          <t>Steady-State Attainment — Trough Concentrations Across Dosing Cycles (ANOVA)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -20942,7 +20930,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Safety Population with ADA Samples</t>
+          <t>PK Population</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -20952,12 +20940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>ADSL, ADIS</t>
+          <t>ADSL, ADPC</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>t_nab_detail.sas</t>
+          <t>t_steady_state.sas</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -20974,303 +20962,315 @@
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>T14.4.14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Table 14.4.14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Urine Pharmacokinetic Parameters — Renal Excretion and Cumulative Recovery</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>PK Population (Subset with Urine PK)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>ADSL, ADPP</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>t_urine_pk.sas</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.1</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.1</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic (PK) Plot — Mean Serum Concentration-Time Profiles</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_profile.sas</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.2</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.2</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Overlaying Individual PK Concentration Profiles</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>PK Population</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPC</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>f_pk_overlay.sas</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>F14.4.3</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Figure 14.4.3</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Mean (SD) Soluble EGFR and cMet Over Time</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>PD Population</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>ADSL, ADPD</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>f_pd_time.sas</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Simulated figure generated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>F14.4.4</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Figure 14.4.4</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Boxplot of Biomarkers at Baseline vs. Response Status</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Full Analysis Set with Biomarker Data</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Oncology only</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>ADSL, ADBM</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>f_biomarker_box.sas</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>First column retained; non-structural cells use XX</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>Simulated figure generated</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.11</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.11</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Soluble Pharmacodynamic Biomarker Change from Baseline Over Time</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>PD Population</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADBM</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>t_pd_bio_chg.sas</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.12</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.12</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Trough PK Concentration (Ctrough) by Cycle — Target Attainment</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>t_ctrough.sas</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.13</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.13</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Steady-State Attainment — Trough Concentrations Across Dosing Cycles (ANOVA)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>PK Population</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPC</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>t_steady_state.sas</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>T14.4.14</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Table 14.4.14</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Urine Pharmacokinetic Parameters — Renal Excretion and Cumulative Recovery</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>PK Population (Subset with Urine PK)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>ADSL, ADPP</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>t_urine_pk.sas</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>First column retained; non-structural cells use XX</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M19"/>
@@ -23663,7 +23663,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>27 April 2026</t>
+          <t>28 April 2026</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">

--- a/output/TFL_TOC_v2.1.0.xlsx
+++ b/output/TFL_TOC_v2.1.0.xlsx
@@ -32055,7 +32055,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Tables and listings preserve structural examples in the first column and use adaptive shell placeholders in non-structural cells. Expandable treatment/group patterns may include ellipsis (...) and a Total column, without concrete sample sizes in headers.</t>
+          <t>Tables and listings preserve structural examples in the first column and use adaptive shell placeholders in non-structural cells. Controlled treatment/group patterns use Group 1, Group 2, and may retain a separate ellipsis (...) expansion column; that expansion column must remain distinct and must not be merged with Overall, Total, HR, or other analytic columns. Header sample sizes remain generic rather than concrete.</t>
         </is>
       </c>
     </row>
@@ -32160,7 +32160,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>28 April 2026</t>
+          <t>29 April 2026</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">

--- a/output/TFL_TOC_v2.1.0.xlsx
+++ b/output/TFL_TOC_v2.1.0.xlsx
@@ -32619,7 +32619,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>The workbook covers CSR Sections 14.1, 14.2, 14.3, 14.4, and 16.2 only; Section 16.1 is out of scope for this generator.</t>
+          <t>The workbook covers CSR Sections 14.1, 14.2, 14.3, 14.4, and 16.2.</t>
         </is>
       </c>
     </row>
@@ -32760,7 +32760,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">

--- a/output/TFL_TOC_v2.1.0.xlsx
+++ b/output/TFL_TOC_v2.1.0.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Summary of Baseline Disease Characteristics</t>
+          <t>Summary of Baseline Oncology Disease Characteristics</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Summary of Baseline Disease Characteristics</t>
+          <t>Summary of Baseline Oncology Disease Characteristics</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Oncology only</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -32760,7 +32760,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
